--- a/StructureDefinition-MedicationRequest.xlsx
+++ b/StructureDefinition-MedicationRequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-30T11:15:13+00:00</t>
+    <t>2024-09-30T11:48:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-MedicationRequest.xlsx
+++ b/StructureDefinition-MedicationRequest.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.5.0</t>
+    <t>1.6.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-30T11:48:36+00:00</t>
+    <t>2024-09-30T11:54:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-MedicationRequest.xlsx
+++ b/StructureDefinition-MedicationRequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-30T11:54:02+00:00</t>
+    <t>2024-10-01T07:24:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-MedicationRequest.xlsx
+++ b/StructureDefinition-MedicationRequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-01T07:24:51+00:00</t>
+    <t>2024-10-02T07:18:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-MedicationRequest.xlsx
+++ b/StructureDefinition-MedicationRequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-02T07:18:59+00:00</t>
+    <t>2024-10-03T15:45:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-MedicationRequest.xlsx
+++ b/StructureDefinition-MedicationRequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-03T15:45:54+00:00</t>
+    <t>2024-10-03T16:09:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-MedicationRequest.xlsx
+++ b/StructureDefinition-MedicationRequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-03T16:09:56+00:00</t>
+    <t>2024-10-03T16:43:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-MedicationRequest.xlsx
+++ b/StructureDefinition-MedicationRequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-03T16:43:05+00:00</t>
+    <t>2024-10-03T16:45:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-MedicationRequest.xlsx
+++ b/StructureDefinition-MedicationRequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-03T16:45:10+00:00</t>
+    <t>2024-10-08T12:11:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-MedicationRequest.xlsx
+++ b/StructureDefinition-MedicationRequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-08T12:11:06+00:00</t>
+    <t>2024-10-08T14:52:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-MedicationRequest.xlsx
+++ b/StructureDefinition-MedicationRequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-08T14:52:43+00:00</t>
+    <t>2024-10-08T15:01:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-MedicationRequest.xlsx
+++ b/StructureDefinition-MedicationRequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-08T15:01:02+00:00</t>
+    <t>2024-10-08T15:17:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-MedicationRequest.xlsx
+++ b/StructureDefinition-MedicationRequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-08T15:17:59+00:00</t>
+    <t>2024-10-14T07:51:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-MedicationRequest.xlsx
+++ b/StructureDefinition-MedicationRequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-14T07:51:32+00:00</t>
+    <t>2024-10-15T11:57:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-MedicationRequest.xlsx
+++ b/StructureDefinition-MedicationRequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-15T11:57:40+00:00</t>
+    <t>2024-10-15T13:32:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-MedicationRequest.xlsx
+++ b/StructureDefinition-MedicationRequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-15T13:32:14+00:00</t>
+    <t>2024-10-17T08:27:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-MedicationRequest.xlsx
+++ b/StructureDefinition-MedicationRequest.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.6.0</t>
+    <t>1.7.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-17T08:27:04+00:00</t>
+    <t>2024-10-17T08:35:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-MedicationRequest.xlsx
+++ b/StructureDefinition-MedicationRequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-17T08:35:21+00:00</t>
+    <t>2024-10-26T09:12:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-MedicationRequest.xlsx
+++ b/StructureDefinition-MedicationRequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-26T09:12:53+00:00</t>
+    <t>2024-10-29T13:54:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-MedicationRequest.xlsx
+++ b/StructureDefinition-MedicationRequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-29T13:54:17+00:00</t>
+    <t>2024-10-30T11:37:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-MedicationRequest.xlsx
+++ b/StructureDefinition-MedicationRequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-30T11:37:59+00:00</t>
+    <t>2024-11-04T07:59:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-MedicationRequest.xlsx
+++ b/StructureDefinition-MedicationRequest.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AS$99</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AS$130</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4075" uniqueCount="641">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5350" uniqueCount="811">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-04T07:59:20+00:00</t>
+    <t>2024-11-06T14:12:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1786,6 +1786,556 @@
     <t>.outboundRelationship[typeCode=COMP].target[classCode=SBADM, moodCode=INT]</t>
   </si>
   <si>
+    <t>MedicationRequest.dosageInstruction.id</t>
+  </si>
+  <si>
+    <t>MedicationRequest.dosageInstruction.extension</t>
+  </si>
+  <si>
+    <t>MedicationRequest.dosageInstruction.sequence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Volgnummer
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">integer
+</t>
+  </si>
+  <si>
+    <t>SequenceNumber</t>
+  </si>
+  <si>
+    <t>This indicates the sequence of the dosing instructions within the medication agreement.</t>
+  </si>
+  <si>
+    <t>If the sequence number of multiple Dosages is the same, then it is implied that the instructions are to be treated as concurrent.  If the sequence number is different, then the Dosages are intended to be sequential.</t>
+  </si>
+  <si>
+    <t>Dosage.sequence</t>
+  </si>
+  <si>
+    <t>.text</t>
+  </si>
+  <si>
+    <t>MedicationRequest.dosageInstruction.text</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Omschrijving
+</t>
+  </si>
+  <si>
+    <t>Textual description of the complete instructions for use including the period of use.</t>
+  </si>
+  <si>
+    <t>Free text dosage instructions can be used for cases where the instructions are too complex to code.  The content of this attribute does not include the name or description of the medication. When coded instructions are present, the free text instructions may still be present for display to humans taking or administering the medication. It is expected that the text instructions will always be populated.  If the dosage.timing attribute is also populated, then the dosage.text should reflect the same information as the timing.</t>
+  </si>
+  <si>
+    <t>Dosage.text</t>
+  </si>
+  <si>
+    <t>MedicationRequest.dosageInstruction.additionalInstruction</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AanvullendeInstructie
+</t>
+  </si>
+  <si>
+    <t>AdditionalInstructions</t>
+  </si>
+  <si>
+    <t>The additional instructions contain extra information on the use of or considerations for the current prescription. This can also include all instructions for use. The text can come from the original 'paper' medication prescription, but can also be generated from the coded information. This concept may contain more information than what is structurally coded in the information below, but may not conflict with it.                  The instructions may not conflict with other components of the request for administration. The instructions can also refer to an existing protocol.                                  The G standard contains many texts that can support this attribute, in for example G standard table 362, which contains texts from the general practitioners’ standard WCIA table 25. If desired, these texts can be used to structure this concept.</t>
+  </si>
+  <si>
+    <t>Additional instruction such as "Swallow with plenty of water" which may or may not be coded.</t>
+  </si>
+  <si>
+    <t>http://decor.nictiz.nl/fhir/ValueSet/2.16.840.1.113883.2.4.3.11.60.20.77.11.9--20160407000000</t>
+  </si>
+  <si>
+    <t>Dosage.additionalInstruction</t>
+  </si>
+  <si>
+    <t>MedicationRequest.dosageInstruction.patientInstruction</t>
+  </si>
+  <si>
+    <t>Patient or consumer oriented instructions</t>
+  </si>
+  <si>
+    <t>Instructions in terms that are understood by the patient or consumer.</t>
+  </si>
+  <si>
+    <t>Dosage.patientInstruction</t>
+  </si>
+  <si>
+    <t>MedicationRequest.dosageInstruction.timing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Toedieningsschema
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Timing {http://nictiz.nl/fhir/StructureDefinition/zib-AdministrationSchedule}
+</t>
+  </si>
+  <si>
+    <t>AdministeringSchedule</t>
+  </si>
+  <si>
+    <t>Specifications of the times at which the medication is to be administered. This is indicated as follows:                  Time(s) (16:00) or indications (“before meals”) at which the medication is to be taken each day.                 A specific number of times the medication is to be taken each day (“3x a day“), indicated with the frequency                 A time interval between consecutive doses (“Every 2 hours”, “every 3 days”), indicated with the word Interval.                 Combined periods with an interval and duration (“1 daily for three out of four weeks: the pill schedule”)                                                   If a certain medication is not to be taken daily, the aforementioned can be combined with daily indications:                  One or more week days on which the medication is to be administered (e.g. “Monday, Wednesday, Friday”)                 ”3x a week”, “2x a month”.                                                   The specified administration “infinite” is automatically to be repeated until:                  The end date and time has been reached                 The total administration duration has been reached (14 days)                                                   A specific amount of administrations has been reached (“20 doses”, “one-time only”), to be entered in the NumberOfDoses concept.</t>
+  </si>
+  <si>
+    <t>A timing schedule can be either a list of events - intervals on which the event occurs, or a single event with repeating criteria or just repeating criteria with no actual event.  When both event and a repeating specification are provided, the list of events should be understood as an interpretation of the information in the repeat structure.</t>
+  </si>
+  <si>
+    <t>The timing schedule for giving the medication to the patient. The Schedule data type allows many different expressions. For example: "Every 8 hours"; "Three times a day"; "1/2 an hour before breakfast for 10 days from 23-Dec 2011:"; "15 Oct 2013, 17 Oct 2013 and 1 Nov 2013".  Sometimes, a rate can imply duration when expressed as total volume / duration (e.g.  500mL/2 hours implies a duration of 2 hours).  However, when rate doesn't imply duration (e.g. 250mL/hour), then the timing.repeat.duration is needed to convey the infuse over time period.</t>
+  </si>
+  <si>
+    <t>Dosage.timing</t>
+  </si>
+  <si>
+    <t>QSET&lt;TS&gt; (GTS)</t>
+  </si>
+  <si>
+    <t>MedicationRequest.dosageInstruction.asNeeded[x]</t>
+  </si>
+  <si>
+    <t>Take "as needed" (for x)</t>
+  </si>
+  <si>
+    <t>Indicates whether the Medication is only taken when needed within a specific dosing schedule (Boolean option), or it indicates the precondition for taking the Medication (CodeableConcept).</t>
+  </si>
+  <si>
+    <t>Can express "as needed" without a reason by setting the Boolean = True.  In this case the CodeableConcept is not populated.  Or you can express "as needed" with a reason by including the CodeableConcept.  In this case the Boolean is assumed to be True.  If you set the Boolean to False, then the dose is given according to the schedule and is not "prn" or "as needed".</t>
+  </si>
+  <si>
+    <t>example</t>
+  </si>
+  <si>
+    <t>A coded concept identifying the precondition that should be met or evaluated prior to consuming or administering a medication dose.  For example "pain", "30 minutes prior to sexual intercourse", "on flare-up" etc.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/medication-as-needed-reason</t>
+  </si>
+  <si>
+    <t>Dosage.asNeeded[x]</t>
+  </si>
+  <si>
+    <t>.outboundRelationship[typeCode=PRCN].target[classCode=OBS, moodCode=EVN, code="as needed"].value=boolean or codable concept</t>
+  </si>
+  <si>
+    <t>MedicationRequest.dosageInstruction.asNeeded[x]:asNeededCodeableConcept</t>
+  </si>
+  <si>
+    <t>asNeededCodeableConcept</t>
+  </si>
+  <si>
+    <t>Zo nodig
+Criterium</t>
+  </si>
+  <si>
+    <t>AsNeeded</t>
+  </si>
+  <si>
+    <t>As needed means that the dose is only to be administered under certain conditions.</t>
+  </si>
+  <si>
+    <t>Using the term 'as needed' or a specific reason (eg 'in case of pain') to use medication leads to ambiguity. It is not always clear whether the whole dose is 'as needed' or only part of the dose. For example: 1x daily 1-2 tablets as needed. This can mean: 1 tablet fixed per day and 1 tablet as needed or, as needed, a maximum of 2 tablets.As needed medication is not included in GDS. In the first situation, 1 tablet comes in the GDS (drug dispensing systems) and 1 tablet is delivered separately. In the second situation there is only separate delivery.The system must make sufficiently clear whether the entire instruction or part of the dose is necessary. The HCIM supports both options described above.</t>
+  </si>
+  <si>
+    <t>ZonodigCriteriumCodelijst</t>
+  </si>
+  <si>
+    <t>http://decor.nictiz.nl/fhir/ValueSet/2.16.840.1.113883.2.4.3.11.60.40.2.9.12.4--20171231000000</t>
+  </si>
+  <si>
+    <t>MedicationRequest.dosageInstruction.site</t>
+  </si>
+  <si>
+    <t>Body site to administer to</t>
+  </si>
+  <si>
+    <t>Body site to administer to.</t>
+  </si>
+  <si>
+    <t>If the use case requires attributes from the BodySite resource (e.g. to identify and track separately) then use the standard extension [body-site-instance](http://hl7.org/fhir/STU3/extension-body-site-instance.html).  May be a summary code, or a reference to a very precise definition of the location, or both.</t>
+  </si>
+  <si>
+    <t>A coded specification of the anatomic site where the medication first enters the body.</t>
+  </si>
+  <si>
+    <t>A coded concept describing the site location the medicine enters into or onto the body.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/approach-site-codes</t>
+  </si>
+  <si>
+    <t>Dosage.site</t>
+  </si>
+  <si>
+    <t>.approachSiteCode</t>
+  </si>
+  <si>
+    <t>MedicationRequest.dosageInstruction.route</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Toedieningsweg
+</t>
+  </si>
+  <si>
+    <t>RouteOfAdministration</t>
+  </si>
+  <si>
+    <t>The route through which the medication is administered (oral, nasal, intravenous, etc.)</t>
+  </si>
+  <si>
+    <t>A code specifying the route or physiological path of administration of a therapeutic agent into or onto a patient's body.</t>
+  </si>
+  <si>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;system value="urn:oid:2.16.840.1.113883.2.4.4.9"/&gt;
+    &lt;code value="oraal"/&gt;
+    &lt;display value="Oraal"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
+  </si>
+  <si>
+    <t>ToedieningswegCodelijst</t>
+  </si>
+  <si>
+    <t>http://decor.nictiz.nl/fhir/ValueSet/2.16.840.1.113883.2.4.3.11.60.40.2.9.12.1--20171231000000</t>
+  </si>
+  <si>
+    <t>Dosage.route</t>
+  </si>
+  <si>
+    <t>.routeCode</t>
+  </si>
+  <si>
+    <t>MedicationRequest.dosageInstruction.route.id</t>
+  </si>
+  <si>
+    <t>MedicationRequest.dosageInstruction.route.extension</t>
+  </si>
+  <si>
+    <t>MedicationRequest.dosageInstruction.route.coding</t>
+  </si>
+  <si>
+    <t>MedicationRequest.dosageInstruction.route.text</t>
+  </si>
+  <si>
+    <t>MedicationRequest.dosageInstruction.method</t>
+  </si>
+  <si>
+    <t>Technique for administering medication</t>
+  </si>
+  <si>
+    <t>Technique for administering medication.</t>
+  </si>
+  <si>
+    <t>Terminologies used often pre-coordinate this term with the route and or form of administration.</t>
+  </si>
+  <si>
+    <t>A coded value indicating the method by which the medication is introduced into or onto the body. Most commonly used for injections.  For examples, Slow Push; Deep IV.</t>
+  </si>
+  <si>
+    <t>A coded concept describing the technique by which the medicine is administered.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/administration-method-codes</t>
+  </si>
+  <si>
+    <t>Dosage.method</t>
+  </si>
+  <si>
+    <t>.doseQuantity</t>
+  </si>
+  <si>
+    <t>MedicationRequest.dosageInstruction.dose[x]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Keerdosis
+</t>
+  </si>
+  <si>
+    <t>Range
+Quantity {SimpleQuantity}</t>
+  </si>
+  <si>
+    <t>Dose</t>
+  </si>
+  <si>
+    <t>The dose indicates the dose amount per administration. 
+The dosage is described in the unit accompanying the product; usually, this is just a number of units or doses. Liquids and other divisible products will usually include a unit of volume (preferably "ml"). 
+In many cases, the prescriber will want to indicate the dose in units of weight of the active ingredient.  
+If only the ingredient is included and not the product, then the amount of that ingredient will be given. Paracetamol 1000mg is equivalent to 2 Paracetamol 500mg tablets or units. 
+The dosage is sometimes given as a calculation, in which the patient’s body weight or body surface area is used as a parameter. The calculation is however no more than an aid in reaching a decision. 
+In the event of constant administration, sometimes the dose is given in addition to the administration speed (infusion rate) (e.g. 20ml in a syringe or 500ml in a bag), but it is often also omitted. 
+A general dosage recommendation such as ‘Use according to protocol’ or ‘See instructions’ can be sufficient. In that case, no dose is given.</t>
+  </si>
+  <si>
+    <t>Note that this specifies the quantity of the specified medication, not the quantity for each active ingredient(s). Each ingredient amount can be communicated in the Medication resource. For example, if one wants to communicate that a tablet was 375 mg, where the dose was one tablet, you can use the Medication resource to document that the tablet was comprised of 375 mg of drug XYZ. Alternatively if the dose was 375 mg, then you may only need to use the Medication resource to indicate this was a tablet. If the example were an IV such as dopamine and you wanted to communicate that 400mg of dopamine was mixed in 500 ml of some IV solution, then this would all be communicated in the Medication resource. If the administration is not intended to be instantaneous (rate is present or timing has a duration), this can be specified to convey the total amount to be administered over the period of time as indicated by the schedule e.g. 500 ml in dose, with timing used to convey that this should be done over 4 hours.</t>
+  </si>
+  <si>
+    <t>The amount of therapeutic or other substance given at one administration event.</t>
+  </si>
+  <si>
+    <t>Dosage.dose[x]</t>
+  </si>
+  <si>
+    <t>MedicationRequest.dosageInstruction.dose[x]:doseQuantity</t>
+  </si>
+  <si>
+    <t>doseQuantity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quantity {SimpleQuantity}
+</t>
+  </si>
+  <si>
+    <t>A fixed quantity (no comparator)</t>
+  </si>
+  <si>
+    <t>The comparator is not used on a SimpleQuantity</t>
+  </si>
+  <si>
+    <t>The context of use may frequently define what kind of quantity this is and therefore what kind of units can be used. The context of use may also restrict the values for the comparator.</t>
+  </si>
+  <si>
+    <t>GstdTabel902</t>
+  </si>
+  <si>
+    <t>http://decor.nictiz.nl/fhir/ValueSet/2.16.840.1.113883.2.4.3.11.60.20.77.11.27--20160830202453</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() | (children().count() &gt; id.count())}
+qty-3:If a code for the unit is present, the system SHALL also be present {code.empty() or system.exists()}sqty-1:The comparator is not used on a SimpleQuantity {comparator.empty()}</t>
+  </si>
+  <si>
+    <t>PQ, IVL&lt;PQ&gt;, MO, CO, depending on the values</t>
+  </si>
+  <si>
+    <t>SN (see also Range) or CQ</t>
+  </si>
+  <si>
+    <t>MedicationRequest.dosageInstruction.dose[x]:doseRange</t>
+  </si>
+  <si>
+    <t>doseRange</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Range
+</t>
+  </si>
+  <si>
+    <t>Amount of medication per dose</t>
+  </si>
+  <si>
+    <t>Amount of medication per dose.</t>
+  </si>
+  <si>
+    <t>MedicationRequest.dosageInstruction.dose[x]:doseRange.id</t>
+  </si>
+  <si>
+    <t>MedicationRequest.dosageInstruction.dose[x].id</t>
+  </si>
+  <si>
+    <t>MedicationRequest.dosageInstruction.dose[x]:doseRange.extension</t>
+  </si>
+  <si>
+    <t>MedicationRequest.dosageInstruction.dose[x].extension</t>
+  </si>
+  <si>
+    <t>MedicationRequest.dosageInstruction.dose[x]:doseRange.low</t>
+  </si>
+  <si>
+    <t>MedicationRequest.dosageInstruction.dose[x].low</t>
+  </si>
+  <si>
+    <t>Low limit</t>
+  </si>
+  <si>
+    <t>The low limit. The boundary is inclusive.</t>
+  </si>
+  <si>
+    <t>If the low element is missing, the low boundary is not known.</t>
+  </si>
+  <si>
+    <t>Range.low</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rng-2
+</t>
+  </si>
+  <si>
+    <t>./low</t>
+  </si>
+  <si>
+    <t>NR.1</t>
+  </si>
+  <si>
+    <t>MedicationRequest.dosageInstruction.dose[x]:doseRange.high</t>
+  </si>
+  <si>
+    <t>MedicationRequest.dosageInstruction.dose[x].high</t>
+  </si>
+  <si>
+    <t>High limit</t>
+  </si>
+  <si>
+    <t>The high limit. The boundary is inclusive.</t>
+  </si>
+  <si>
+    <t>If the high element is missing, the high boundary is not known.</t>
+  </si>
+  <si>
+    <t>Range.high</t>
+  </si>
+  <si>
+    <t>./high</t>
+  </si>
+  <si>
+    <t>NR.2</t>
+  </si>
+  <si>
+    <t>MedicationRequest.dosageInstruction.maxDosePerPeriod</t>
+  </si>
+  <si>
+    <t>Maximale dosering
+Maximale dosis (per dag enz.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ratio
+</t>
+  </si>
+  <si>
+    <t>MaximumDose</t>
+  </si>
+  <si>
+    <t>A maximum dose indicates the maximum duration a product can be used with an ‘as needed’ prescription.
+For example:
+- Max 6 units per day
+- Max 200ml per week</t>
+  </si>
+  <si>
+    <t>This is intended for use as an adjunct to the dosage when there is an upper cap.  For example "2 tablets every 4 hours to a maximum of 8/day".</t>
+  </si>
+  <si>
+    <t>The maximum total quantity of a therapeutic substance that may be administered to a subject over the period of time.  For example, 1000mg in 24 hours.</t>
+  </si>
+  <si>
+    <t>Dosage.maxDosePerPeriod</t>
+  </si>
+  <si>
+    <t>.maxDoseQuantity</t>
+  </si>
+  <si>
+    <t>MedicationRequest.dosageInstruction.maxDosePerPeriod.id</t>
+  </si>
+  <si>
+    <t>MedicationRequest.dosageInstruction.maxDosePerPeriod.extension</t>
+  </si>
+  <si>
+    <t>MedicationRequest.dosageInstruction.maxDosePerPeriod.numerator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quantity
+</t>
+  </si>
+  <si>
+    <t>Numerator value</t>
+  </si>
+  <si>
+    <t>The value of the numerator.</t>
+  </si>
+  <si>
+    <t>Ratio.numerator</t>
+  </si>
+  <si>
+    <t>.numerator</t>
+  </si>
+  <si>
+    <t>MedicationRequest.dosageInstruction.maxDosePerPeriod.denominator</t>
+  </si>
+  <si>
+    <t>Denominator value</t>
+  </si>
+  <si>
+    <t>The value of the denominator.</t>
+  </si>
+  <si>
+    <t>Ratio.denominator</t>
+  </si>
+  <si>
+    <t>.denominator</t>
+  </si>
+  <si>
+    <t>MedicationRequest.dosageInstruction.maxDosePerAdministration</t>
+  </si>
+  <si>
+    <t>Upper limit on medication per administration</t>
+  </si>
+  <si>
+    <t>Upper limit on medication per administration.</t>
+  </si>
+  <si>
+    <t>This is intended for use as an adjunct to the dosage when there is an upper cap.  For example, a body surface area related dose with a maximum amount, such as 1.5 mg/m2 (maximum 2 mg) IV over 5 – 10 minutes would have doseQuantity of 1.5 mg/m2 and maxDosePerAdministration of 2 mg.</t>
+  </si>
+  <si>
+    <t>The maximum total quantity of a therapeutic substance that may be administered to a subject per administration.</t>
+  </si>
+  <si>
+    <t>Dosage.maxDosePerAdministration</t>
+  </si>
+  <si>
+    <t>not supported</t>
+  </si>
+  <si>
+    <t>MedicationRequest.dosageInstruction.maxDosePerLifetime</t>
+  </si>
+  <si>
+    <t>Upper limit on medication per lifetime of the patient</t>
+  </si>
+  <si>
+    <t>Upper limit on medication per lifetime of the patient.</t>
+  </si>
+  <si>
+    <t>The maximum total quantity of a therapeutic substance that may be administered per lifetime of the subject.</t>
+  </si>
+  <si>
+    <t>Dosage.maxDosePerLifetime</t>
+  </si>
+  <si>
+    <t>MedicationRequest.dosageInstruction.rate[x]</t>
+  </si>
+  <si>
+    <t>Toedieningssnelheid
+Inloopsnelheid</t>
+  </si>
+  <si>
+    <t>Ratio
+RangeQuantity {SimpleQuantity}</t>
+  </si>
+  <si>
+    <t>AdministeringSpeed</t>
+  </si>
+  <si>
+    <t>The administering speed is used in slow administration of liquid. In practice, the measuring unit is almost always ml/hour. Entering an interval (such as 0-10 ml/hour) is also a commonly used option. For example, with an administering speed of 10ml/hour: amount = 10, dose unit = ml                 time unit = hour</t>
+  </si>
+  <si>
+    <t>It is possible to supply both a rate and a doseQuantity to provide full details about how the medication is to be administered and supplied. If the rate is intended to change over time, depending on local rules/regulations, each change should be captured as a new version of the MedicationRequest with an updated rate, or captured with a new MedicationRequest with the new rate.</t>
+  </si>
+  <si>
+    <t>Identifies the speed with which the medication was or will be introduced into the patient. Typically the rate for an infusion e.g. 100 ml per 1 hour or 100 ml/hr.  May also be expressed as a rate per unit of time e.g. 500 ml per 2 hours.   Other examples: 200 mcg/min or 200 mcg/1 minute; 1 liter/8 hours.  Sometimes, a rate can imply duration when expressed as total volume / duration (e.g.  500mL/2 hours implies a duration of 2 hours).  However, when rate doesn't imply duration (e.g. 250mL/hour), then the timing.repeat.duration is needed to convey the infuse over time period.</t>
+  </si>
+  <si>
+    <t>Dosage.rate[x]</t>
+  </si>
+  <si>
+    <t>.rateQuantity</t>
+  </si>
+  <si>
     <t>MedicationRequest.dispenseRequest</t>
   </si>
   <si>
@@ -1863,10 +2413,6 @@
     <t>MedicationRequest.dispenseRequest.quantity</t>
   </si>
   <si>
-    <t xml:space="preserve">Quantity {SimpleQuantity}
-</t>
-  </si>
-  <si>
     <t>Amount of medication to supply per dispense</t>
   </si>
   <si>
@@ -1969,9 +2515,6 @@
   </si>
   <si>
     <t>Indicates the reason for the substitution, or why substitution must or must not be performed.</t>
-  </si>
-  <si>
-    <t>example</t>
   </si>
   <si>
     <t>A coded concept describing the reason that a different medication should (or should not) be substituted from what was prescribed.</t>
@@ -2372,11 +2915,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AS99"/>
+  <dimension ref="A1:AS130"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="78.44921875" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="59.37890625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="65.9453125" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="28.30078125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="30.078125" customWidth="true" bestFit="true"/>
@@ -2399,7 +2942,7 @@
     <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="121.76953125" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="198.02734375" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="90.54296875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
@@ -8237,7 +8780,7 @@
         <v>95</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="I46" t="s" s="2">
         <v>85</v>
@@ -9779,7 +10322,7 @@
         <v>95</v>
       </c>
       <c r="H58" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="I58" t="s" s="2">
         <v>85</v>
@@ -12868,13 +13411,13 @@
         <v>85</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>462</v>
+        <v>172</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>557</v>
+        <v>173</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>558</v>
+        <v>174</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" s="2"/>
@@ -12925,7 +13468,7 @@
         <v>85</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>556</v>
+        <v>175</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>83</v>
@@ -12937,7 +13480,7 @@
         <v>85</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>552</v>
+        <v>85</v>
       </c>
       <c r="AK82" t="s" s="2">
         <v>85</v>
@@ -12955,10 +13498,10 @@
         <v>85</v>
       </c>
       <c r="AP82" t="s" s="2">
-        <v>559</v>
+        <v>85</v>
       </c>
       <c r="AQ82" t="s" s="2">
-        <v>560</v>
+        <v>176</v>
       </c>
       <c r="AR82" t="s" s="2">
         <v>85</v>
@@ -12969,21 +13512,21 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>561</v>
+        <v>557</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>561</v>
+        <v>557</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
-        <v>85</v>
+        <v>179</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H83" t="s" s="2">
         <v>85</v>
@@ -12995,15 +13538,17 @@
         <v>85</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="N83" s="2"/>
+        <v>181</v>
+      </c>
+      <c r="N83" t="s" s="2">
+        <v>182</v>
+      </c>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
         <v>85</v>
@@ -13040,25 +13585,25 @@
         <v>85</v>
       </c>
       <c r="AB83" t="s" s="2">
-        <v>85</v>
+        <v>143</v>
       </c>
       <c r="AC83" t="s" s="2">
-        <v>85</v>
+        <v>183</v>
       </c>
       <c r="AD83" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AE83" t="s" s="2">
-        <v>85</v>
+        <v>144</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>175</v>
+        <v>184</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH83" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI83" t="s" s="2">
         <v>85</v>
@@ -13096,21 +13641,21 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
-        <v>179</v>
+        <v>559</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G84" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H84" t="s" s="2">
         <v>85</v>
@@ -13119,21 +13664,21 @@
         <v>85</v>
       </c>
       <c r="J84" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>140</v>
+        <v>560</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>180</v>
+        <v>561</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>181</v>
-      </c>
-      <c r="N84" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="O84" s="2"/>
+        <v>562</v>
+      </c>
+      <c r="N84" s="2"/>
+      <c r="O84" t="s" s="2">
+        <v>563</v>
+      </c>
       <c r="P84" t="s" s="2">
         <v>85</v>
       </c>
@@ -13181,13 +13726,13 @@
         <v>85</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>184</v>
+        <v>564</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH84" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI84" t="s" s="2">
         <v>85</v>
@@ -13214,7 +13759,7 @@
         <v>85</v>
       </c>
       <c r="AQ84" t="s" s="2">
-        <v>176</v>
+        <v>565</v>
       </c>
       <c r="AR84" t="s" s="2">
         <v>85</v>
@@ -13225,44 +13770,44 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
-        <v>474</v>
+        <v>567</v>
       </c>
       <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G85" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H85" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="I85" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="J85" t="s" s="2">
         <v>96</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>140</v>
+        <v>172</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>475</v>
+        <v>21</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>476</v>
-      </c>
-      <c r="N85" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="O85" s="2"/>
+        <v>568</v>
+      </c>
+      <c r="N85" s="2"/>
+      <c r="O85" t="s" s="2">
+        <v>569</v>
+      </c>
       <c r="P85" t="s" s="2">
         <v>85</v>
       </c>
@@ -13310,13 +13855,13 @@
         <v>85</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>477</v>
+        <v>570</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH85" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI85" t="s" s="2">
         <v>85</v>
@@ -13343,7 +13888,7 @@
         <v>85</v>
       </c>
       <c r="AQ85" t="s" s="2">
-        <v>138</v>
+        <v>565</v>
       </c>
       <c r="AR85" t="s" s="2">
         <v>85</v>
@@ -13354,21 +13899,21 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>564</v>
+        <v>571</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>564</v>
+        <v>571</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
-        <v>85</v>
+        <v>572</v>
       </c>
       <c r="E86" s="2"/>
       <c r="F86" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G86" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H86" t="s" s="2">
         <v>85</v>
@@ -13377,22 +13922,20 @@
         <v>85</v>
       </c>
       <c r="J86" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>565</v>
+        <v>194</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>566</v>
+        <v>573</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>567</v>
-      </c>
-      <c r="N86" t="s" s="2">
-        <v>568</v>
-      </c>
+        <v>574</v>
+      </c>
+      <c r="N86" s="2"/>
       <c r="O86" t="s" s="2">
-        <v>569</v>
+        <v>575</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>85</v>
@@ -13417,13 +13960,11 @@
         <v>85</v>
       </c>
       <c r="X86" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="Y86" t="s" s="2">
-        <v>85</v>
-      </c>
+        <v>118</v>
+      </c>
+      <c r="Y86" s="2"/>
       <c r="Z86" t="s" s="2">
-        <v>85</v>
+        <v>576</v>
       </c>
       <c r="AA86" t="s" s="2">
         <v>85</v>
@@ -13441,13 +13982,13 @@
         <v>85</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>564</v>
+        <v>577</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH86" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI86" t="s" s="2">
         <v>85</v>
@@ -13471,10 +14012,10 @@
         <v>85</v>
       </c>
       <c r="AP86" t="s" s="2">
-        <v>570</v>
+        <v>85</v>
       </c>
       <c r="AQ86" t="s" s="2">
-        <v>571</v>
+        <v>565</v>
       </c>
       <c r="AR86" t="s" s="2">
         <v>85</v>
@@ -13485,10 +14026,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>572</v>
+        <v>578</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>572</v>
+        <v>578</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -13508,20 +14049,18 @@
         <v>85</v>
       </c>
       <c r="J87" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>573</v>
+        <v>172</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>575</v>
-      </c>
-      <c r="N87" t="s" s="2">
-        <v>576</v>
-      </c>
+        <v>580</v>
+      </c>
+      <c r="N87" s="2"/>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
         <v>85</v>
@@ -13570,7 +14109,7 @@
         <v>85</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>572</v>
+        <v>581</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>83</v>
@@ -13600,28 +14139,28 @@
         <v>85</v>
       </c>
       <c r="AP87" t="s" s="2">
-        <v>577</v>
+        <v>85</v>
       </c>
       <c r="AQ87" t="s" s="2">
-        <v>578</v>
+        <v>565</v>
       </c>
       <c r="AR87" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS87" t="s" s="2">
-        <v>579</v>
+        <v>85</v>
       </c>
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
-        <v>85</v>
+        <v>583</v>
       </c>
       <c r="E88" s="2"/>
       <c r="F88" t="s" s="2">
@@ -13640,16 +14179,20 @@
         <v>85</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>583</v>
-      </c>
-      <c r="N88" s="2"/>
-      <c r="O88" s="2"/>
+        <v>586</v>
+      </c>
+      <c r="N88" t="s" s="2">
+        <v>587</v>
+      </c>
+      <c r="O88" t="s" s="2">
+        <v>588</v>
+      </c>
       <c r="P88" t="s" s="2">
         <v>85</v>
       </c>
@@ -13697,7 +14240,7 @@
         <v>85</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>580</v>
+        <v>589</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>83</v>
@@ -13706,10 +14249,10 @@
         <v>95</v>
       </c>
       <c r="AI88" t="s" s="2">
-        <v>85</v>
+        <v>153</v>
       </c>
       <c r="AJ88" t="s" s="2">
-        <v>85</v>
+        <v>552</v>
       </c>
       <c r="AK88" t="s" s="2">
         <v>85</v>
@@ -13727,24 +14270,24 @@
         <v>85</v>
       </c>
       <c r="AP88" t="s" s="2">
-        <v>584</v>
+        <v>85</v>
       </c>
       <c r="AQ88" t="s" s="2">
-        <v>585</v>
+        <v>590</v>
       </c>
       <c r="AR88" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS88" t="s" s="2">
-        <v>586</v>
+        <v>138</v>
       </c>
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>587</v>
+        <v>591</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>587</v>
+        <v>591</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13764,19 +14307,19 @@
         <v>85</v>
       </c>
       <c r="J89" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>588</v>
+        <v>194</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>590</v>
+        <v>593</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
@@ -13802,31 +14345,29 @@
         <v>85</v>
       </c>
       <c r="X89" t="s" s="2">
-        <v>85</v>
+        <v>595</v>
       </c>
       <c r="Y89" t="s" s="2">
-        <v>85</v>
+        <v>596</v>
       </c>
       <c r="Z89" t="s" s="2">
-        <v>85</v>
+        <v>597</v>
       </c>
       <c r="AA89" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AB89" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AC89" t="s" s="2">
-        <v>85</v>
-      </c>
+        <v>197</v>
+      </c>
+      <c r="AC89" s="2"/>
       <c r="AD89" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AE89" t="s" s="2">
-        <v>85</v>
+        <v>198</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>587</v>
+        <v>598</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>83</v>
@@ -13856,10 +14397,10 @@
         <v>85</v>
       </c>
       <c r="AP89" t="s" s="2">
-        <v>592</v>
+        <v>85</v>
       </c>
       <c r="AQ89" t="s" s="2">
-        <v>593</v>
+        <v>599</v>
       </c>
       <c r="AR89" t="s" s="2">
         <v>85</v>
@@ -13870,14 +14411,16 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>594</v>
+        <v>600</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>594</v>
-      </c>
-      <c r="C90" s="2"/>
+        <v>591</v>
+      </c>
+      <c r="C90" t="s" s="2">
+        <v>601</v>
+      </c>
       <c r="D90" t="s" s="2">
-        <v>85</v>
+        <v>602</v>
       </c>
       <c r="E90" s="2"/>
       <c r="F90" t="s" s="2">
@@ -13893,18 +14436,20 @@
         <v>85</v>
       </c>
       <c r="J90" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>595</v>
+        <v>194</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>596</v>
+        <v>603</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>597</v>
-      </c>
-      <c r="N90" s="2"/>
+        <v>604</v>
+      </c>
+      <c r="N90" t="s" s="2">
+        <v>605</v>
+      </c>
       <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
         <v>85</v>
@@ -13929,13 +14474,13 @@
         <v>85</v>
       </c>
       <c r="X90" t="s" s="2">
-        <v>85</v>
+        <v>118</v>
       </c>
       <c r="Y90" t="s" s="2">
-        <v>85</v>
+        <v>606</v>
       </c>
       <c r="Z90" t="s" s="2">
-        <v>85</v>
+        <v>607</v>
       </c>
       <c r="AA90" t="s" s="2">
         <v>85</v>
@@ -13953,7 +14498,7 @@
         <v>85</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>594</v>
+        <v>598</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>83</v>
@@ -13986,10 +14531,10 @@
         <v>85</v>
       </c>
       <c r="AQ90" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="AR90" t="s" s="2">
-        <v>508</v>
+        <v>85</v>
       </c>
       <c r="AS90" t="s" s="2">
         <v>85</v>
@@ -13997,10 +14542,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>599</v>
+        <v>608</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>599</v>
+        <v>608</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -14020,19 +14565,23 @@
         <v>85</v>
       </c>
       <c r="J91" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>462</v>
+        <v>194</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>600</v>
+        <v>609</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>601</v>
-      </c>
-      <c r="N91" s="2"/>
-      <c r="O91" s="2"/>
+        <v>610</v>
+      </c>
+      <c r="N91" t="s" s="2">
+        <v>611</v>
+      </c>
+      <c r="O91" t="s" s="2">
+        <v>612</v>
+      </c>
       <c r="P91" t="s" s="2">
         <v>85</v>
       </c>
@@ -14056,13 +14605,13 @@
         <v>85</v>
       </c>
       <c r="X91" t="s" s="2">
-        <v>85</v>
+        <v>595</v>
       </c>
       <c r="Y91" t="s" s="2">
-        <v>85</v>
+        <v>613</v>
       </c>
       <c r="Z91" t="s" s="2">
-        <v>85</v>
+        <v>614</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>85</v>
@@ -14080,7 +14629,7 @@
         <v>85</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>599</v>
+        <v>615</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>83</v>
@@ -14092,7 +14641,7 @@
         <v>85</v>
       </c>
       <c r="AJ91" t="s" s="2">
-        <v>552</v>
+        <v>85</v>
       </c>
       <c r="AK91" t="s" s="2">
         <v>85</v>
@@ -14110,10 +14659,10 @@
         <v>85</v>
       </c>
       <c r="AP91" t="s" s="2">
-        <v>602</v>
+        <v>85</v>
       </c>
       <c r="AQ91" t="s" s="2">
-        <v>603</v>
+        <v>616</v>
       </c>
       <c r="AR91" t="s" s="2">
         <v>85</v>
@@ -14124,14 +14673,14 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>604</v>
+        <v>617</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>604</v>
+        <v>617</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
-        <v>85</v>
+        <v>618</v>
       </c>
       <c r="E92" s="2"/>
       <c r="F92" t="s" s="2">
@@ -14147,19 +14696,21 @@
         <v>85</v>
       </c>
       <c r="J92" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>172</v>
+        <v>194</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>173</v>
+        <v>619</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>174</v>
+        <v>620</v>
       </c>
       <c r="N92" s="2"/>
-      <c r="O92" s="2"/>
+      <c r="O92" t="s" s="2">
+        <v>621</v>
+      </c>
       <c r="P92" t="s" s="2">
         <v>85</v>
       </c>
@@ -14171,7 +14722,7 @@
         <v>85</v>
       </c>
       <c r="T92" t="s" s="2">
-        <v>85</v>
+        <v>622</v>
       </c>
       <c r="U92" t="s" s="2">
         <v>85</v>
@@ -14183,13 +14734,13 @@
         <v>85</v>
       </c>
       <c r="X92" t="s" s="2">
-        <v>85</v>
+        <v>118</v>
       </c>
       <c r="Y92" t="s" s="2">
-        <v>85</v>
+        <v>623</v>
       </c>
       <c r="Z92" t="s" s="2">
-        <v>85</v>
+        <v>624</v>
       </c>
       <c r="AA92" t="s" s="2">
         <v>85</v>
@@ -14207,7 +14758,7 @@
         <v>85</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>175</v>
+        <v>625</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>83</v>
@@ -14240,7 +14791,7 @@
         <v>85</v>
       </c>
       <c r="AQ92" t="s" s="2">
-        <v>176</v>
+        <v>626</v>
       </c>
       <c r="AR92" t="s" s="2">
         <v>85</v>
@@ -14251,21 +14802,21 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>605</v>
+        <v>627</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>605</v>
+        <v>627</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
-        <v>179</v>
+        <v>85</v>
       </c>
       <c r="E93" s="2"/>
       <c r="F93" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G93" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H93" t="s" s="2">
         <v>85</v>
@@ -14277,17 +14828,15 @@
         <v>85</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>140</v>
+        <v>172</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>181</v>
-      </c>
-      <c r="N93" t="s" s="2">
-        <v>182</v>
-      </c>
+        <v>174</v>
+      </c>
+      <c r="N93" s="2"/>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
         <v>85</v>
@@ -14336,13 +14885,13 @@
         <v>85</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH93" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI93" t="s" s="2">
         <v>85</v>
@@ -14380,14 +14929,14 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>606</v>
+        <v>628</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>606</v>
+        <v>628</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
-        <v>474</v>
+        <v>179</v>
       </c>
       <c r="E94" s="2"/>
       <c r="F94" t="s" s="2">
@@ -14400,19 +14949,19 @@
         <v>85</v>
       </c>
       <c r="I94" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="J94" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K94" t="s" s="2">
         <v>140</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>475</v>
+        <v>180</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>476</v>
+        <v>181</v>
       </c>
       <c r="N94" t="s" s="2">
         <v>182</v>
@@ -14453,19 +15002,19 @@
         <v>85</v>
       </c>
       <c r="AB94" t="s" s="2">
-        <v>85</v>
+        <v>143</v>
       </c>
       <c r="AC94" t="s" s="2">
-        <v>85</v>
+        <v>183</v>
       </c>
       <c r="AD94" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AE94" t="s" s="2">
-        <v>85</v>
+        <v>144</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>477</v>
+        <v>184</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>83</v>
@@ -14498,7 +15047,7 @@
         <v>85</v>
       </c>
       <c r="AQ94" t="s" s="2">
-        <v>138</v>
+        <v>176</v>
       </c>
       <c r="AR94" t="s" s="2">
         <v>85</v>
@@ -14509,10 +15058,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>607</v>
+        <v>629</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>607</v>
+        <v>629</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -14520,33 +15069,35 @@
       </c>
       <c r="E95" s="2"/>
       <c r="F95" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="G95" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H95" t="s" s="2">
         <v>85</v>
       </c>
       <c r="I95" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="J95" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="J95" t="s" s="2">
-        <v>85</v>
-      </c>
       <c r="K95" t="s" s="2">
-        <v>360</v>
+        <v>306</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>608</v>
+        <v>307</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>609</v>
+        <v>308</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>610</v>
-      </c>
-      <c r="O95" s="2"/>
+        <v>309</v>
+      </c>
+      <c r="O95" t="s" s="2">
+        <v>310</v>
+      </c>
       <c r="P95" t="s" s="2">
         <v>85</v>
       </c>
@@ -14594,13 +15145,13 @@
         <v>85</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>607</v>
+        <v>312</v>
       </c>
       <c r="AG95" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="AH95" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI95" t="s" s="2">
         <v>85</v>
@@ -14624,24 +15175,24 @@
         <v>85</v>
       </c>
       <c r="AP95" t="s" s="2">
-        <v>602</v>
+        <v>85</v>
       </c>
       <c r="AQ95" t="s" s="2">
-        <v>611</v>
+        <v>313</v>
       </c>
       <c r="AR95" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS95" t="s" s="2">
-        <v>612</v>
+        <v>314</v>
       </c>
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>613</v>
+        <v>630</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>613</v>
+        <v>630</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -14655,25 +15206,29 @@
         <v>95</v>
       </c>
       <c r="H96" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="I96" t="s" s="2">
         <v>85</v>
       </c>
       <c r="J96" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>194</v>
+        <v>172</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>614</v>
+        <v>369</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>615</v>
-      </c>
-      <c r="N96" s="2"/>
-      <c r="O96" s="2"/>
+        <v>370</v>
+      </c>
+      <c r="N96" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="O96" t="s" s="2">
+        <v>372</v>
+      </c>
       <c r="P96" t="s" s="2">
         <v>85</v>
       </c>
@@ -14697,13 +15252,13 @@
         <v>85</v>
       </c>
       <c r="X96" t="s" s="2">
-        <v>616</v>
+        <v>85</v>
       </c>
       <c r="Y96" t="s" s="2">
-        <v>617</v>
+        <v>85</v>
       </c>
       <c r="Z96" t="s" s="2">
-        <v>618</v>
+        <v>85</v>
       </c>
       <c r="AA96" t="s" s="2">
         <v>85</v>
@@ -14721,7 +15276,7 @@
         <v>85</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>613</v>
+        <v>373</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>83</v>
@@ -14751,24 +15306,24 @@
         <v>85</v>
       </c>
       <c r="AP96" t="s" s="2">
-        <v>619</v>
+        <v>85</v>
       </c>
       <c r="AQ96" t="s" s="2">
-        <v>620</v>
+        <v>374</v>
       </c>
       <c r="AR96" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS96" t="s" s="2">
-        <v>621</v>
+        <v>375</v>
       </c>
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>622</v>
+        <v>631</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>622</v>
+        <v>631</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14788,19 +15343,23 @@
         <v>85</v>
       </c>
       <c r="J97" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>623</v>
+        <v>194</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>624</v>
+        <v>632</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>625</v>
-      </c>
-      <c r="N97" s="2"/>
-      <c r="O97" s="2"/>
+        <v>633</v>
+      </c>
+      <c r="N97" t="s" s="2">
+        <v>634</v>
+      </c>
+      <c r="O97" t="s" s="2">
+        <v>635</v>
+      </c>
       <c r="P97" t="s" s="2">
         <v>85</v>
       </c>
@@ -14824,13 +15383,13 @@
         <v>85</v>
       </c>
       <c r="X97" t="s" s="2">
-        <v>85</v>
+        <v>595</v>
       </c>
       <c r="Y97" t="s" s="2">
-        <v>85</v>
+        <v>636</v>
       </c>
       <c r="Z97" t="s" s="2">
-        <v>85</v>
+        <v>637</v>
       </c>
       <c r="AA97" t="s" s="2">
         <v>85</v>
@@ -14848,7 +15407,7 @@
         <v>85</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>622</v>
+        <v>638</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>83</v>
@@ -14875,13 +15434,13 @@
         <v>85</v>
       </c>
       <c r="AO97" t="s" s="2">
-        <v>626</v>
+        <v>85</v>
       </c>
       <c r="AP97" t="s" s="2">
-        <v>619</v>
+        <v>85</v>
       </c>
       <c r="AQ97" t="s" s="2">
-        <v>627</v>
+        <v>639</v>
       </c>
       <c r="AR97" t="s" s="2">
         <v>85</v>
@@ -14892,21 +15451,21 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>628</v>
+        <v>640</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>628</v>
+        <v>640</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
-        <v>629</v>
+        <v>641</v>
       </c>
       <c r="E98" s="2"/>
       <c r="F98" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G98" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H98" t="s" s="2">
         <v>85</v>
@@ -14915,19 +15474,23 @@
         <v>85</v>
       </c>
       <c r="J98" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>630</v>
+        <v>642</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>631</v>
+        <v>643</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>632</v>
-      </c>
-      <c r="N98" s="2"/>
-      <c r="O98" s="2"/>
+        <v>644</v>
+      </c>
+      <c r="N98" t="s" s="2">
+        <v>645</v>
+      </c>
+      <c r="O98" t="s" s="2">
+        <v>646</v>
+      </c>
       <c r="P98" t="s" s="2">
         <v>85</v>
       </c>
@@ -14963,25 +15526,23 @@
         <v>85</v>
       </c>
       <c r="AB98" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AC98" t="s" s="2">
-        <v>85</v>
-      </c>
+        <v>197</v>
+      </c>
+      <c r="AC98" s="2"/>
       <c r="AD98" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AE98" t="s" s="2">
-        <v>85</v>
+        <v>198</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>628</v>
+        <v>647</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH98" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI98" t="s" s="2">
         <v>85</v>
@@ -15008,7 +15569,7 @@
         <v>85</v>
       </c>
       <c r="AQ98" t="s" s="2">
-        <v>633</v>
+        <v>639</v>
       </c>
       <c r="AR98" t="s" s="2">
         <v>85</v>
@@ -15019,12 +15580,14 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>634</v>
+        <v>648</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>634</v>
-      </c>
-      <c r="C99" s="2"/>
+        <v>640</v>
+      </c>
+      <c r="C99" t="s" s="2">
+        <v>649</v>
+      </c>
       <c r="D99" t="s" s="2">
         <v>85</v>
       </c>
@@ -15033,7 +15596,7 @@
         <v>83</v>
       </c>
       <c r="G99" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H99" t="s" s="2">
         <v>85</v>
@@ -15045,18 +15608,20 @@
         <v>85</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>635</v>
+        <v>650</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>636</v>
+        <v>651</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>637</v>
+        <v>652</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>638</v>
-      </c>
-      <c r="O99" s="2"/>
+        <v>653</v>
+      </c>
+      <c r="O99" t="s" s="2">
+        <v>646</v>
+      </c>
       <c r="P99" t="s" s="2">
         <v>85</v>
       </c>
@@ -15080,13 +15645,13 @@
         <v>85</v>
       </c>
       <c r="X99" t="s" s="2">
-        <v>85</v>
+        <v>238</v>
       </c>
       <c r="Y99" t="s" s="2">
-        <v>85</v>
+        <v>654</v>
       </c>
       <c r="Z99" t="s" s="2">
-        <v>85</v>
+        <v>655</v>
       </c>
       <c r="AA99" t="s" s="2">
         <v>85</v>
@@ -15104,50 +15669,4035 @@
         <v>85</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>634</v>
+        <v>647</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH99" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AI99" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="AJ99" t="s" s="2">
+        <v>656</v>
+      </c>
+      <c r="AK99" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AL99" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AM99" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AN99" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AO99" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AP99" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AQ99" t="s" s="2">
+        <v>657</v>
+      </c>
+      <c r="AR99" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AS99" t="s" s="2">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="100" hidden="true">
+      <c r="A100" t="s" s="2">
+        <v>659</v>
+      </c>
+      <c r="B100" t="s" s="2">
+        <v>640</v>
+      </c>
+      <c r="C100" t="s" s="2">
+        <v>660</v>
+      </c>
+      <c r="D100" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="E100" s="2"/>
+      <c r="F100" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="G100" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="H100" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="I100" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="J100" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="K100" t="s" s="2">
+        <v>661</v>
+      </c>
+      <c r="L100" t="s" s="2">
+        <v>662</v>
+      </c>
+      <c r="M100" t="s" s="2">
+        <v>663</v>
+      </c>
+      <c r="N100" t="s" s="2">
+        <v>645</v>
+      </c>
+      <c r="O100" t="s" s="2">
+        <v>646</v>
+      </c>
+      <c r="P100" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Q100" s="2"/>
+      <c r="R100" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="S100" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="T100" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="U100" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="V100" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="W100" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="X100" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Y100" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Z100" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AA100" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB100" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AC100" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AD100" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AE100" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AF100" t="s" s="2">
+        <v>647</v>
+      </c>
+      <c r="AG100" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH100" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AI100" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AJ100" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AK100" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AL100" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AM100" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AN100" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AO100" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AP100" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AQ100" t="s" s="2">
+        <v>639</v>
+      </c>
+      <c r="AR100" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AS100" t="s" s="2">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="101" hidden="true">
+      <c r="A101" t="s" s="2">
+        <v>664</v>
+      </c>
+      <c r="B101" t="s" s="2">
+        <v>665</v>
+      </c>
+      <c r="C101" s="2"/>
+      <c r="D101" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="E101" s="2"/>
+      <c r="F101" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="G101" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="H101" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="I101" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="J101" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="K101" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="L101" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="M101" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="N101" s="2"/>
+      <c r="O101" s="2"/>
+      <c r="P101" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Q101" s="2"/>
+      <c r="R101" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="S101" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="T101" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="U101" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="V101" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="W101" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="X101" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Y101" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Z101" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AA101" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB101" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AC101" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AD101" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AE101" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AF101" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="AG101" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH101" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AI101" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AJ101" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AK101" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AL101" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AM101" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AN101" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AO101" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AP101" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AQ101" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="AR101" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AS101" t="s" s="2">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="102" hidden="true">
+      <c r="A102" t="s" s="2">
+        <v>666</v>
+      </c>
+      <c r="B102" t="s" s="2">
+        <v>667</v>
+      </c>
+      <c r="C102" s="2"/>
+      <c r="D102" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="E102" s="2"/>
+      <c r="F102" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="G102" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="AI99" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AJ99" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AK99" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AL99" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AM99" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AN99" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AO99" t="s" s="2">
-        <v>639</v>
-      </c>
-      <c r="AP99" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AQ99" t="s" s="2">
-        <v>640</v>
-      </c>
-      <c r="AR99" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AS99" t="s" s="2">
+      <c r="H102" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="I102" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="J102" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="K102" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="L102" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="M102" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="N102" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="O102" s="2"/>
+      <c r="P102" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Q102" s="2"/>
+      <c r="R102" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="S102" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="T102" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="U102" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="V102" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="W102" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="X102" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Y102" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Z102" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AA102" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB102" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="AC102" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="AD102" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AE102" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="AF102" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="AG102" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH102" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI102" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AJ102" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AK102" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AL102" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AM102" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AN102" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AO102" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AP102" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AQ102" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="AR102" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AS102" t="s" s="2">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="103" hidden="true">
+      <c r="A103" t="s" s="2">
+        <v>668</v>
+      </c>
+      <c r="B103" t="s" s="2">
+        <v>669</v>
+      </c>
+      <c r="C103" s="2"/>
+      <c r="D103" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="E103" s="2"/>
+      <c r="F103" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="G103" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="H103" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="I103" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="J103" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="K103" t="s" s="2">
+        <v>650</v>
+      </c>
+      <c r="L103" t="s" s="2">
+        <v>670</v>
+      </c>
+      <c r="M103" t="s" s="2">
+        <v>671</v>
+      </c>
+      <c r="N103" t="s" s="2">
+        <v>672</v>
+      </c>
+      <c r="O103" s="2"/>
+      <c r="P103" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Q103" s="2"/>
+      <c r="R103" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="S103" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="T103" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="U103" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="V103" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="W103" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="X103" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="Y103" t="s" s="2">
+        <v>654</v>
+      </c>
+      <c r="Z103" t="s" s="2">
+        <v>655</v>
+      </c>
+      <c r="AA103" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB103" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AC103" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AD103" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AE103" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AF103" t="s" s="2">
+        <v>673</v>
+      </c>
+      <c r="AG103" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH103" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AI103" t="s" s="2">
+        <v>674</v>
+      </c>
+      <c r="AJ103" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AK103" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AL103" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AM103" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AN103" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AO103" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AP103" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AQ103" t="s" s="2">
+        <v>675</v>
+      </c>
+      <c r="AR103" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AS103" t="s" s="2">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="104" hidden="true">
+      <c r="A104" t="s" s="2">
+        <v>677</v>
+      </c>
+      <c r="B104" t="s" s="2">
+        <v>678</v>
+      </c>
+      <c r="C104" s="2"/>
+      <c r="D104" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="E104" s="2"/>
+      <c r="F104" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="G104" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="H104" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="I104" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="J104" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="K104" t="s" s="2">
+        <v>650</v>
+      </c>
+      <c r="L104" t="s" s="2">
+        <v>679</v>
+      </c>
+      <c r="M104" t="s" s="2">
+        <v>680</v>
+      </c>
+      <c r="N104" t="s" s="2">
+        <v>681</v>
+      </c>
+      <c r="O104" s="2"/>
+      <c r="P104" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Q104" s="2"/>
+      <c r="R104" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="S104" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="T104" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="U104" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="V104" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="W104" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="X104" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="Y104" t="s" s="2">
+        <v>654</v>
+      </c>
+      <c r="Z104" t="s" s="2">
+        <v>655</v>
+      </c>
+      <c r="AA104" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB104" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AC104" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AD104" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AE104" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AF104" t="s" s="2">
+        <v>682</v>
+      </c>
+      <c r="AG104" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH104" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AI104" t="s" s="2">
+        <v>674</v>
+      </c>
+      <c r="AJ104" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AK104" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AL104" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AM104" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AN104" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AO104" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AP104" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AQ104" t="s" s="2">
+        <v>683</v>
+      </c>
+      <c r="AR104" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AS104" t="s" s="2">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="105" hidden="true">
+      <c r="A105" t="s" s="2">
+        <v>685</v>
+      </c>
+      <c r="B105" t="s" s="2">
+        <v>685</v>
+      </c>
+      <c r="C105" s="2"/>
+      <c r="D105" t="s" s="2">
+        <v>686</v>
+      </c>
+      <c r="E105" s="2"/>
+      <c r="F105" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="G105" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="H105" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="I105" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="J105" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="K105" t="s" s="2">
+        <v>687</v>
+      </c>
+      <c r="L105" t="s" s="2">
+        <v>688</v>
+      </c>
+      <c r="M105" t="s" s="2">
+        <v>689</v>
+      </c>
+      <c r="N105" t="s" s="2">
+        <v>690</v>
+      </c>
+      <c r="O105" t="s" s="2">
+        <v>691</v>
+      </c>
+      <c r="P105" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Q105" s="2"/>
+      <c r="R105" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="S105" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="T105" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="U105" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="V105" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="W105" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="X105" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Y105" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Z105" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AA105" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB105" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AC105" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AD105" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AE105" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AF105" t="s" s="2">
+        <v>692</v>
+      </c>
+      <c r="AG105" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH105" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AI105" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AJ105" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AK105" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AL105" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AM105" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AN105" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AO105" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AP105" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AQ105" t="s" s="2">
+        <v>693</v>
+      </c>
+      <c r="AR105" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AS105" t="s" s="2">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="106" hidden="true">
+      <c r="A106" t="s" s="2">
+        <v>694</v>
+      </c>
+      <c r="B106" t="s" s="2">
+        <v>694</v>
+      </c>
+      <c r="C106" s="2"/>
+      <c r="D106" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="E106" s="2"/>
+      <c r="F106" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="G106" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="H106" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="I106" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="J106" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="K106" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="L106" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="M106" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="N106" s="2"/>
+      <c r="O106" s="2"/>
+      <c r="P106" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Q106" s="2"/>
+      <c r="R106" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="S106" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="T106" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="U106" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="V106" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="W106" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="X106" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Y106" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Z106" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AA106" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB106" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AC106" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AD106" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AE106" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AF106" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="AG106" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH106" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AI106" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AJ106" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AK106" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AL106" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AM106" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AN106" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AO106" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AP106" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AQ106" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="AR106" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AS106" t="s" s="2">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="107" hidden="true">
+      <c r="A107" t="s" s="2">
+        <v>695</v>
+      </c>
+      <c r="B107" t="s" s="2">
+        <v>695</v>
+      </c>
+      <c r="C107" s="2"/>
+      <c r="D107" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="E107" s="2"/>
+      <c r="F107" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="G107" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H107" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="I107" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="J107" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="K107" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="L107" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="M107" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="N107" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="O107" s="2"/>
+      <c r="P107" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Q107" s="2"/>
+      <c r="R107" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="S107" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="T107" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="U107" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="V107" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="W107" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="X107" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Y107" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Z107" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AA107" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB107" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="AC107" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="AD107" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AE107" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="AF107" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="AG107" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH107" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI107" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AJ107" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AK107" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AL107" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AM107" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AN107" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AO107" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AP107" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AQ107" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="AR107" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AS107" t="s" s="2">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="108" hidden="true">
+      <c r="A108" t="s" s="2">
+        <v>696</v>
+      </c>
+      <c r="B108" t="s" s="2">
+        <v>696</v>
+      </c>
+      <c r="C108" s="2"/>
+      <c r="D108" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="E108" s="2"/>
+      <c r="F108" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="G108" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="H108" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="I108" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="J108" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="K108" t="s" s="2">
+        <v>697</v>
+      </c>
+      <c r="L108" t="s" s="2">
+        <v>698</v>
+      </c>
+      <c r="M108" t="s" s="2">
+        <v>699</v>
+      </c>
+      <c r="N108" s="2"/>
+      <c r="O108" s="2"/>
+      <c r="P108" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Q108" s="2"/>
+      <c r="R108" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="S108" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="T108" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="U108" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="V108" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="W108" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="X108" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="Y108" t="s" s="2">
+        <v>654</v>
+      </c>
+      <c r="Z108" t="s" s="2">
+        <v>655</v>
+      </c>
+      <c r="AA108" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB108" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AC108" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AD108" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AE108" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AF108" t="s" s="2">
+        <v>700</v>
+      </c>
+      <c r="AG108" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH108" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AI108" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AJ108" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AK108" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AL108" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AM108" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AN108" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AO108" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AP108" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AQ108" t="s" s="2">
+        <v>701</v>
+      </c>
+      <c r="AR108" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AS108" t="s" s="2">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="109" hidden="true">
+      <c r="A109" t="s" s="2">
+        <v>702</v>
+      </c>
+      <c r="B109" t="s" s="2">
+        <v>702</v>
+      </c>
+      <c r="C109" s="2"/>
+      <c r="D109" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="E109" s="2"/>
+      <c r="F109" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="G109" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="H109" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="I109" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="J109" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="K109" t="s" s="2">
+        <v>697</v>
+      </c>
+      <c r="L109" t="s" s="2">
+        <v>703</v>
+      </c>
+      <c r="M109" t="s" s="2">
+        <v>704</v>
+      </c>
+      <c r="N109" s="2"/>
+      <c r="O109" s="2"/>
+      <c r="P109" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Q109" s="2"/>
+      <c r="R109" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="S109" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="T109" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="U109" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="V109" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="W109" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="X109" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Y109" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Z109" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AA109" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB109" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AC109" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AD109" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AE109" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AF109" t="s" s="2">
+        <v>705</v>
+      </c>
+      <c r="AG109" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH109" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AI109" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AJ109" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AK109" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AL109" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AM109" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AN109" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AO109" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AP109" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AQ109" t="s" s="2">
+        <v>706</v>
+      </c>
+      <c r="AR109" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AS109" t="s" s="2">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="110" hidden="true">
+      <c r="A110" t="s" s="2">
+        <v>707</v>
+      </c>
+      <c r="B110" t="s" s="2">
+        <v>707</v>
+      </c>
+      <c r="C110" s="2"/>
+      <c r="D110" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="E110" s="2"/>
+      <c r="F110" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="G110" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="H110" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="I110" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="J110" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="K110" t="s" s="2">
+        <v>650</v>
+      </c>
+      <c r="L110" t="s" s="2">
+        <v>708</v>
+      </c>
+      <c r="M110" t="s" s="2">
+        <v>709</v>
+      </c>
+      <c r="N110" t="s" s="2">
+        <v>710</v>
+      </c>
+      <c r="O110" t="s" s="2">
+        <v>711</v>
+      </c>
+      <c r="P110" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Q110" s="2"/>
+      <c r="R110" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="S110" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="T110" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="U110" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="V110" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="W110" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="X110" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Y110" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Z110" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AA110" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB110" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AC110" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AD110" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AE110" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AF110" t="s" s="2">
+        <v>712</v>
+      </c>
+      <c r="AG110" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH110" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AI110" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AJ110" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AK110" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AL110" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AM110" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AN110" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AO110" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AP110" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AQ110" t="s" s="2">
+        <v>713</v>
+      </c>
+      <c r="AR110" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AS110" t="s" s="2">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="111" hidden="true">
+      <c r="A111" t="s" s="2">
+        <v>714</v>
+      </c>
+      <c r="B111" t="s" s="2">
+        <v>714</v>
+      </c>
+      <c r="C111" s="2"/>
+      <c r="D111" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="E111" s="2"/>
+      <c r="F111" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="G111" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="H111" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="I111" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="J111" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="K111" t="s" s="2">
+        <v>650</v>
+      </c>
+      <c r="L111" t="s" s="2">
+        <v>715</v>
+      </c>
+      <c r="M111" t="s" s="2">
+        <v>716</v>
+      </c>
+      <c r="N111" s="2"/>
+      <c r="O111" t="s" s="2">
+        <v>717</v>
+      </c>
+      <c r="P111" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Q111" s="2"/>
+      <c r="R111" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="S111" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="T111" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="U111" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="V111" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="W111" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="X111" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Y111" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Z111" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AA111" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB111" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AC111" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AD111" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AE111" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AF111" t="s" s="2">
+        <v>718</v>
+      </c>
+      <c r="AG111" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH111" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AI111" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AJ111" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AK111" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AL111" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AM111" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AN111" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AO111" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AP111" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AQ111" t="s" s="2">
+        <v>713</v>
+      </c>
+      <c r="AR111" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AS111" t="s" s="2">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="112" hidden="true">
+      <c r="A112" t="s" s="2">
+        <v>719</v>
+      </c>
+      <c r="B112" t="s" s="2">
+        <v>719</v>
+      </c>
+      <c r="C112" s="2"/>
+      <c r="D112" t="s" s="2">
+        <v>720</v>
+      </c>
+      <c r="E112" s="2"/>
+      <c r="F112" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="G112" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="H112" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="I112" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="J112" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="K112" t="s" s="2">
+        <v>721</v>
+      </c>
+      <c r="L112" t="s" s="2">
+        <v>722</v>
+      </c>
+      <c r="M112" t="s" s="2">
+        <v>723</v>
+      </c>
+      <c r="N112" t="s" s="2">
+        <v>724</v>
+      </c>
+      <c r="O112" t="s" s="2">
+        <v>725</v>
+      </c>
+      <c r="P112" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Q112" s="2"/>
+      <c r="R112" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="S112" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="T112" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="U112" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="V112" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="W112" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="X112" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Y112" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Z112" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AA112" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB112" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AC112" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AD112" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AE112" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AF112" t="s" s="2">
+        <v>726</v>
+      </c>
+      <c r="AG112" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH112" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AI112" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AJ112" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AK112" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AL112" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AM112" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AN112" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AO112" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AP112" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AQ112" t="s" s="2">
+        <v>727</v>
+      </c>
+      <c r="AR112" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AS112" t="s" s="2">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="113" hidden="true">
+      <c r="A113" t="s" s="2">
+        <v>728</v>
+      </c>
+      <c r="B113" t="s" s="2">
+        <v>728</v>
+      </c>
+      <c r="C113" s="2"/>
+      <c r="D113" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="E113" s="2"/>
+      <c r="F113" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="G113" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="H113" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="I113" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="J113" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="K113" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="L113" t="s" s="2">
+        <v>729</v>
+      </c>
+      <c r="M113" t="s" s="2">
+        <v>730</v>
+      </c>
+      <c r="N113" s="2"/>
+      <c r="O113" s="2"/>
+      <c r="P113" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Q113" s="2"/>
+      <c r="R113" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="S113" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="T113" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="U113" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="V113" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="W113" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="X113" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Y113" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Z113" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AA113" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB113" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AC113" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AD113" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AE113" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AF113" t="s" s="2">
+        <v>728</v>
+      </c>
+      <c r="AG113" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH113" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AI113" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AJ113" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="AK113" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AL113" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AM113" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AN113" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AO113" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AP113" t="s" s="2">
+        <v>731</v>
+      </c>
+      <c r="AQ113" t="s" s="2">
+        <v>732</v>
+      </c>
+      <c r="AR113" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AS113" t="s" s="2">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="114" hidden="true">
+      <c r="A114" t="s" s="2">
+        <v>733</v>
+      </c>
+      <c r="B114" t="s" s="2">
+        <v>733</v>
+      </c>
+      <c r="C114" s="2"/>
+      <c r="D114" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="E114" s="2"/>
+      <c r="F114" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="G114" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="H114" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="I114" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="J114" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="K114" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="L114" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="M114" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="N114" s="2"/>
+      <c r="O114" s="2"/>
+      <c r="P114" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Q114" s="2"/>
+      <c r="R114" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="S114" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="T114" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="U114" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="V114" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="W114" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="X114" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Y114" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Z114" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AA114" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB114" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AC114" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AD114" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AE114" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AF114" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="AG114" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH114" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AI114" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AJ114" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AK114" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AL114" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AM114" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AN114" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AO114" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AP114" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AQ114" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="AR114" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AS114" t="s" s="2">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="115" hidden="true">
+      <c r="A115" t="s" s="2">
+        <v>734</v>
+      </c>
+      <c r="B115" t="s" s="2">
+        <v>734</v>
+      </c>
+      <c r="C115" s="2"/>
+      <c r="D115" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="E115" s="2"/>
+      <c r="F115" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="G115" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H115" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="I115" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="J115" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="K115" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="L115" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="M115" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="N115" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="O115" s="2"/>
+      <c r="P115" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Q115" s="2"/>
+      <c r="R115" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="S115" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="T115" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="U115" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="V115" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="W115" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="X115" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Y115" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Z115" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AA115" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB115" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AC115" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AD115" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AE115" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AF115" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="AG115" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH115" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI115" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AJ115" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AK115" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AL115" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AM115" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AN115" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AO115" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AP115" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AQ115" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="AR115" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AS115" t="s" s="2">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="116" hidden="true">
+      <c r="A116" t="s" s="2">
+        <v>735</v>
+      </c>
+      <c r="B116" t="s" s="2">
+        <v>735</v>
+      </c>
+      <c r="C116" s="2"/>
+      <c r="D116" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="E116" s="2"/>
+      <c r="F116" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="G116" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H116" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="I116" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="J116" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="K116" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="L116" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="M116" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="N116" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="O116" s="2"/>
+      <c r="P116" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Q116" s="2"/>
+      <c r="R116" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="S116" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="T116" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="U116" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="V116" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="W116" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="X116" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Y116" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Z116" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AA116" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB116" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AC116" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AD116" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AE116" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AF116" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="AG116" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH116" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI116" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AJ116" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AK116" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AL116" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AM116" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AN116" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AO116" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AP116" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AQ116" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="AR116" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AS116" t="s" s="2">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="117" hidden="true">
+      <c r="A117" t="s" s="2">
+        <v>736</v>
+      </c>
+      <c r="B117" t="s" s="2">
+        <v>736</v>
+      </c>
+      <c r="C117" s="2"/>
+      <c r="D117" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="E117" s="2"/>
+      <c r="F117" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="G117" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="H117" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="I117" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="J117" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="K117" t="s" s="2">
+        <v>737</v>
+      </c>
+      <c r="L117" t="s" s="2">
+        <v>738</v>
+      </c>
+      <c r="M117" t="s" s="2">
+        <v>739</v>
+      </c>
+      <c r="N117" t="s" s="2">
+        <v>740</v>
+      </c>
+      <c r="O117" t="s" s="2">
+        <v>741</v>
+      </c>
+      <c r="P117" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Q117" s="2"/>
+      <c r="R117" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="S117" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="T117" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="U117" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="V117" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="W117" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="X117" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Y117" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Z117" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AA117" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB117" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AC117" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AD117" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AE117" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AF117" t="s" s="2">
+        <v>736</v>
+      </c>
+      <c r="AG117" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH117" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AI117" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AJ117" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AK117" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AL117" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AM117" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AN117" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AO117" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AP117" t="s" s="2">
+        <v>742</v>
+      </c>
+      <c r="AQ117" t="s" s="2">
+        <v>743</v>
+      </c>
+      <c r="AR117" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AS117" t="s" s="2">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="118" hidden="true">
+      <c r="A118" t="s" s="2">
+        <v>744</v>
+      </c>
+      <c r="B118" t="s" s="2">
+        <v>744</v>
+      </c>
+      <c r="C118" s="2"/>
+      <c r="D118" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="E118" s="2"/>
+      <c r="F118" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="G118" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="H118" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="I118" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="J118" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="K118" t="s" s="2">
+        <v>745</v>
+      </c>
+      <c r="L118" t="s" s="2">
+        <v>746</v>
+      </c>
+      <c r="M118" t="s" s="2">
+        <v>747</v>
+      </c>
+      <c r="N118" t="s" s="2">
+        <v>748</v>
+      </c>
+      <c r="O118" s="2"/>
+      <c r="P118" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Q118" s="2"/>
+      <c r="R118" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="S118" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="T118" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="U118" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="V118" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="W118" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="X118" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Y118" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Z118" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AA118" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB118" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AC118" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AD118" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AE118" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AF118" t="s" s="2">
+        <v>744</v>
+      </c>
+      <c r="AG118" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH118" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AI118" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AJ118" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AK118" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AL118" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AM118" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AN118" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AO118" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AP118" t="s" s="2">
+        <v>749</v>
+      </c>
+      <c r="AQ118" t="s" s="2">
+        <v>750</v>
+      </c>
+      <c r="AR118" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AS118" t="s" s="2">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="119" hidden="true">
+      <c r="A119" t="s" s="2">
+        <v>752</v>
+      </c>
+      <c r="B119" t="s" s="2">
+        <v>752</v>
+      </c>
+      <c r="C119" s="2"/>
+      <c r="D119" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="E119" s="2"/>
+      <c r="F119" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="G119" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="H119" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="I119" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="J119" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="K119" t="s" s="2">
+        <v>650</v>
+      </c>
+      <c r="L119" t="s" s="2">
+        <v>753</v>
+      </c>
+      <c r="M119" t="s" s="2">
+        <v>754</v>
+      </c>
+      <c r="N119" s="2"/>
+      <c r="O119" s="2"/>
+      <c r="P119" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Q119" s="2"/>
+      <c r="R119" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="S119" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="T119" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="U119" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="V119" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="W119" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="X119" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Y119" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Z119" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AA119" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB119" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AC119" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AD119" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AE119" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AF119" t="s" s="2">
+        <v>752</v>
+      </c>
+      <c r="AG119" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH119" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AI119" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AJ119" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AK119" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AL119" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AM119" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AN119" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AO119" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AP119" t="s" s="2">
+        <v>755</v>
+      </c>
+      <c r="AQ119" t="s" s="2">
+        <v>756</v>
+      </c>
+      <c r="AR119" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AS119" t="s" s="2">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="120" hidden="true">
+      <c r="A120" t="s" s="2">
+        <v>758</v>
+      </c>
+      <c r="B120" t="s" s="2">
+        <v>758</v>
+      </c>
+      <c r="C120" s="2"/>
+      <c r="D120" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="E120" s="2"/>
+      <c r="F120" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="G120" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="H120" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="I120" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="J120" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="K120" t="s" s="2">
+        <v>759</v>
+      </c>
+      <c r="L120" t="s" s="2">
+        <v>760</v>
+      </c>
+      <c r="M120" t="s" s="2">
+        <v>761</v>
+      </c>
+      <c r="N120" t="s" s="2">
+        <v>762</v>
+      </c>
+      <c r="O120" s="2"/>
+      <c r="P120" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Q120" s="2"/>
+      <c r="R120" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="S120" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="T120" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="U120" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="V120" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="W120" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="X120" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Y120" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Z120" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AA120" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB120" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AC120" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AD120" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AE120" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AF120" t="s" s="2">
+        <v>758</v>
+      </c>
+      <c r="AG120" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH120" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AI120" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AJ120" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AK120" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AL120" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AM120" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AN120" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AO120" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AP120" t="s" s="2">
+        <v>763</v>
+      </c>
+      <c r="AQ120" t="s" s="2">
+        <v>764</v>
+      </c>
+      <c r="AR120" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AS120" t="s" s="2">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="121" hidden="true">
+      <c r="A121" t="s" s="2">
+        <v>765</v>
+      </c>
+      <c r="B121" t="s" s="2">
+        <v>765</v>
+      </c>
+      <c r="C121" s="2"/>
+      <c r="D121" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="E121" s="2"/>
+      <c r="F121" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="G121" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="H121" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="I121" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="J121" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="K121" t="s" s="2">
+        <v>766</v>
+      </c>
+      <c r="L121" t="s" s="2">
+        <v>767</v>
+      </c>
+      <c r="M121" t="s" s="2">
+        <v>768</v>
+      </c>
+      <c r="N121" s="2"/>
+      <c r="O121" s="2"/>
+      <c r="P121" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Q121" s="2"/>
+      <c r="R121" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="S121" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="T121" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="U121" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="V121" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="W121" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="X121" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Y121" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Z121" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AA121" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB121" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AC121" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AD121" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AE121" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AF121" t="s" s="2">
+        <v>765</v>
+      </c>
+      <c r="AG121" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH121" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AI121" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AJ121" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AK121" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AL121" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AM121" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AN121" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AO121" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AP121" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AQ121" t="s" s="2">
+        <v>769</v>
+      </c>
+      <c r="AR121" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="AS121" t="s" s="2">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="122" hidden="true">
+      <c r="A122" t="s" s="2">
+        <v>770</v>
+      </c>
+      <c r="B122" t="s" s="2">
+        <v>770</v>
+      </c>
+      <c r="C122" s="2"/>
+      <c r="D122" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="E122" s="2"/>
+      <c r="F122" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="G122" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="H122" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="I122" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="J122" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="K122" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="L122" t="s" s="2">
+        <v>771</v>
+      </c>
+      <c r="M122" t="s" s="2">
+        <v>772</v>
+      </c>
+      <c r="N122" s="2"/>
+      <c r="O122" s="2"/>
+      <c r="P122" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Q122" s="2"/>
+      <c r="R122" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="S122" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="T122" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="U122" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="V122" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="W122" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="X122" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Y122" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Z122" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AA122" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB122" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AC122" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AD122" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AE122" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AF122" t="s" s="2">
+        <v>770</v>
+      </c>
+      <c r="AG122" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH122" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AI122" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AJ122" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="AK122" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AL122" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AM122" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AN122" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AO122" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AP122" t="s" s="2">
+        <v>773</v>
+      </c>
+      <c r="AQ122" t="s" s="2">
+        <v>774</v>
+      </c>
+      <c r="AR122" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AS122" t="s" s="2">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="123" hidden="true">
+      <c r="A123" t="s" s="2">
+        <v>775</v>
+      </c>
+      <c r="B123" t="s" s="2">
+        <v>775</v>
+      </c>
+      <c r="C123" s="2"/>
+      <c r="D123" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="E123" s="2"/>
+      <c r="F123" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="G123" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="H123" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="I123" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="J123" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="K123" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="L123" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="M123" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="N123" s="2"/>
+      <c r="O123" s="2"/>
+      <c r="P123" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Q123" s="2"/>
+      <c r="R123" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="S123" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="T123" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="U123" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="V123" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="W123" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="X123" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Y123" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Z123" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AA123" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB123" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AC123" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AD123" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AE123" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AF123" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="AG123" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH123" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AI123" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AJ123" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AK123" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AL123" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AM123" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AN123" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AO123" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AP123" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AQ123" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="AR123" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AS123" t="s" s="2">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="124" hidden="true">
+      <c r="A124" t="s" s="2">
+        <v>776</v>
+      </c>
+      <c r="B124" t="s" s="2">
+        <v>776</v>
+      </c>
+      <c r="C124" s="2"/>
+      <c r="D124" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="E124" s="2"/>
+      <c r="F124" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="G124" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H124" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="I124" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="J124" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="K124" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="L124" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="M124" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="N124" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="O124" s="2"/>
+      <c r="P124" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Q124" s="2"/>
+      <c r="R124" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="S124" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="T124" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="U124" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="V124" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="W124" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="X124" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Y124" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Z124" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AA124" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB124" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AC124" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AD124" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AE124" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AF124" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="AG124" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH124" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI124" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AJ124" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AK124" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AL124" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AM124" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AN124" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AO124" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AP124" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AQ124" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="AR124" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AS124" t="s" s="2">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="125" hidden="true">
+      <c r="A125" t="s" s="2">
+        <v>777</v>
+      </c>
+      <c r="B125" t="s" s="2">
+        <v>777</v>
+      </c>
+      <c r="C125" s="2"/>
+      <c r="D125" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="E125" s="2"/>
+      <c r="F125" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="G125" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H125" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="I125" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="J125" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="K125" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="L125" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="M125" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="N125" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="O125" s="2"/>
+      <c r="P125" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Q125" s="2"/>
+      <c r="R125" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="S125" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="T125" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="U125" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="V125" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="W125" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="X125" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Y125" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Z125" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AA125" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB125" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AC125" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AD125" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AE125" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AF125" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="AG125" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH125" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI125" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AJ125" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AK125" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AL125" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AM125" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AN125" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AO125" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AP125" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AQ125" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="AR125" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AS125" t="s" s="2">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="126" hidden="true">
+      <c r="A126" t="s" s="2">
+        <v>778</v>
+      </c>
+      <c r="B126" t="s" s="2">
+        <v>778</v>
+      </c>
+      <c r="C126" s="2"/>
+      <c r="D126" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="E126" s="2"/>
+      <c r="F126" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="G126" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="H126" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="I126" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="J126" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="K126" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="L126" t="s" s="2">
+        <v>779</v>
+      </c>
+      <c r="M126" t="s" s="2">
+        <v>780</v>
+      </c>
+      <c r="N126" t="s" s="2">
+        <v>781</v>
+      </c>
+      <c r="O126" s="2"/>
+      <c r="P126" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Q126" s="2"/>
+      <c r="R126" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="S126" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="T126" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="U126" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="V126" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="W126" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="X126" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Y126" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Z126" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AA126" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB126" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AC126" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AD126" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AE126" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AF126" t="s" s="2">
+        <v>778</v>
+      </c>
+      <c r="AG126" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AH126" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AI126" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AJ126" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AK126" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AL126" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AM126" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AN126" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AO126" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AP126" t="s" s="2">
+        <v>773</v>
+      </c>
+      <c r="AQ126" t="s" s="2">
+        <v>782</v>
+      </c>
+      <c r="AR126" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AS126" t="s" s="2">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="127" hidden="true">
+      <c r="A127" t="s" s="2">
+        <v>784</v>
+      </c>
+      <c r="B127" t="s" s="2">
+        <v>784</v>
+      </c>
+      <c r="C127" s="2"/>
+      <c r="D127" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="E127" s="2"/>
+      <c r="F127" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="G127" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="H127" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="I127" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="J127" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="K127" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="L127" t="s" s="2">
+        <v>785</v>
+      </c>
+      <c r="M127" t="s" s="2">
+        <v>786</v>
+      </c>
+      <c r="N127" s="2"/>
+      <c r="O127" s="2"/>
+      <c r="P127" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Q127" s="2"/>
+      <c r="R127" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="S127" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="T127" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="U127" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="V127" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="W127" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="X127" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="Y127" t="s" s="2">
+        <v>787</v>
+      </c>
+      <c r="Z127" t="s" s="2">
+        <v>788</v>
+      </c>
+      <c r="AA127" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB127" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AC127" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AD127" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AE127" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AF127" t="s" s="2">
+        <v>784</v>
+      </c>
+      <c r="AG127" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH127" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AI127" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AJ127" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AK127" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AL127" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AM127" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AN127" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AO127" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AP127" t="s" s="2">
+        <v>789</v>
+      </c>
+      <c r="AQ127" t="s" s="2">
+        <v>790</v>
+      </c>
+      <c r="AR127" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AS127" t="s" s="2">
+        <v>791</v>
+      </c>
+    </row>
+    <row r="128" hidden="true">
+      <c r="A128" t="s" s="2">
+        <v>792</v>
+      </c>
+      <c r="B128" t="s" s="2">
+        <v>792</v>
+      </c>
+      <c r="C128" s="2"/>
+      <c r="D128" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="E128" s="2"/>
+      <c r="F128" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="G128" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="H128" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="I128" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="J128" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="K128" t="s" s="2">
+        <v>793</v>
+      </c>
+      <c r="L128" t="s" s="2">
+        <v>794</v>
+      </c>
+      <c r="M128" t="s" s="2">
+        <v>795</v>
+      </c>
+      <c r="N128" s="2"/>
+      <c r="O128" s="2"/>
+      <c r="P128" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Q128" s="2"/>
+      <c r="R128" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="S128" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="T128" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="U128" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="V128" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="W128" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="X128" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Y128" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Z128" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AA128" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB128" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AC128" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AD128" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AE128" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AF128" t="s" s="2">
+        <v>792</v>
+      </c>
+      <c r="AG128" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH128" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AI128" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AJ128" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AK128" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AL128" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AM128" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AN128" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AO128" t="s" s="2">
+        <v>796</v>
+      </c>
+      <c r="AP128" t="s" s="2">
+        <v>789</v>
+      </c>
+      <c r="AQ128" t="s" s="2">
+        <v>797</v>
+      </c>
+      <c r="AR128" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AS128" t="s" s="2">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="129" hidden="true">
+      <c r="A129" t="s" s="2">
+        <v>798</v>
+      </c>
+      <c r="B129" t="s" s="2">
+        <v>798</v>
+      </c>
+      <c r="C129" s="2"/>
+      <c r="D129" t="s" s="2">
+        <v>799</v>
+      </c>
+      <c r="E129" s="2"/>
+      <c r="F129" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="G129" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H129" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="I129" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="J129" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="K129" t="s" s="2">
+        <v>800</v>
+      </c>
+      <c r="L129" t="s" s="2">
+        <v>801</v>
+      </c>
+      <c r="M129" t="s" s="2">
+        <v>802</v>
+      </c>
+      <c r="N129" s="2"/>
+      <c r="O129" s="2"/>
+      <c r="P129" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Q129" s="2"/>
+      <c r="R129" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="S129" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="T129" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="U129" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="V129" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="W129" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="X129" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Y129" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Z129" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AA129" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB129" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AC129" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AD129" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AE129" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AF129" t="s" s="2">
+        <v>798</v>
+      </c>
+      <c r="AG129" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH129" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI129" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AJ129" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AK129" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AL129" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AM129" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AN129" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AO129" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AP129" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AQ129" t="s" s="2">
+        <v>803</v>
+      </c>
+      <c r="AR129" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AS129" t="s" s="2">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="130" hidden="true">
+      <c r="A130" t="s" s="2">
+        <v>804</v>
+      </c>
+      <c r="B130" t="s" s="2">
+        <v>804</v>
+      </c>
+      <c r="C130" s="2"/>
+      <c r="D130" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="E130" s="2"/>
+      <c r="F130" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="G130" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H130" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="I130" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="J130" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="K130" t="s" s="2">
+        <v>805</v>
+      </c>
+      <c r="L130" t="s" s="2">
+        <v>806</v>
+      </c>
+      <c r="M130" t="s" s="2">
+        <v>807</v>
+      </c>
+      <c r="N130" t="s" s="2">
+        <v>808</v>
+      </c>
+      <c r="O130" s="2"/>
+      <c r="P130" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Q130" s="2"/>
+      <c r="R130" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="S130" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="T130" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="U130" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="V130" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="W130" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="X130" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Y130" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Z130" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AA130" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB130" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AC130" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AD130" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AE130" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AF130" t="s" s="2">
+        <v>804</v>
+      </c>
+      <c r="AG130" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH130" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI130" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AJ130" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AK130" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AL130" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AM130" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AN130" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AO130" t="s" s="2">
+        <v>809</v>
+      </c>
+      <c r="AP130" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AQ130" t="s" s="2">
+        <v>810</v>
+      </c>
+      <c r="AR130" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AS130" t="s" s="2">
         <v>85</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AS99">
+  <autoFilter ref="A1:AS130">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -15157,7 +19707,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI98">
+  <conditionalFormatting sqref="A2:AI129">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/StructureDefinition-MedicationRequest.xlsx
+++ b/StructureDefinition-MedicationRequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-06T14:12:43+00:00</t>
+    <t>2024-11-06T21:19:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-MedicationRequest.xlsx
+++ b/StructureDefinition-MedicationRequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-06T21:19:30+00:00</t>
+    <t>2024-11-12T08:18:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-MedicationRequest.xlsx
+++ b/StructureDefinition-MedicationRequest.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.7.0</t>
+    <t>1.8.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T08:18:00+00:00</t>
+    <t>2024-11-12T08:24:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-MedicationRequest.xlsx
+++ b/StructureDefinition-MedicationRequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T08:24:06+00:00</t>
+    <t>2024-11-12T10:55:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-MedicationRequest.xlsx
+++ b/StructureDefinition-MedicationRequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T10:55:49+00:00</t>
+    <t>2024-11-12T11:26:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-MedicationRequest.xlsx
+++ b/StructureDefinition-MedicationRequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T11:26:12+00:00</t>
+    <t>2024-11-12T16:51:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-MedicationRequest.xlsx
+++ b/StructureDefinition-MedicationRequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T16:51:17+00:00</t>
+    <t>2024-11-19T12:47:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-MedicationRequest.xlsx
+++ b/StructureDefinition-MedicationRequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-19T12:47:37+00:00</t>
+    <t>2024-11-19T15:01:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-MedicationRequest.xlsx
+++ b/StructureDefinition-MedicationRequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-19T15:01:01+00:00</t>
+    <t>2024-11-24T09:20:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-MedicationRequest.xlsx
+++ b/StructureDefinition-MedicationRequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-24T09:20:45+00:00</t>
+    <t>2024-11-25T09:16:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -8780,7 +8780,7 @@
         <v>95</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="I46" t="s" s="2">
         <v>85</v>

--- a/StructureDefinition-MedicationRequest.xlsx
+++ b/StructureDefinition-MedicationRequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-25T09:16:03+00:00</t>
+    <t>2024-11-25T09:33:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-MedicationRequest.xlsx
+++ b/StructureDefinition-MedicationRequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-25T09:33:17+00:00</t>
+    <t>2024-11-25T09:37:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-MedicationRequest.xlsx
+++ b/StructureDefinition-MedicationRequest.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.8.0</t>
+    <t>1.9.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-25T09:37:54+00:00</t>
+    <t>2024-11-25T09:42:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-MedicationRequest.xlsx
+++ b/StructureDefinition-MedicationRequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-25T09:42:11+00:00</t>
+    <t>2024-11-25T11:02:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-MedicationRequest.xlsx
+++ b/StructureDefinition-MedicationRequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-25T11:02:10+00:00</t>
+    <t>2024-11-28T08:25:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-MedicationRequest.xlsx
+++ b/StructureDefinition-MedicationRequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-28T08:25:00+00:00</t>
+    <t>2024-11-28T17:50:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-MedicationRequest.xlsx
+++ b/StructureDefinition-MedicationRequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-28T17:50:24+00:00</t>
+    <t>2024-11-30T09:54:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-MedicationRequest.xlsx
+++ b/StructureDefinition-MedicationRequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-30T09:54:10+00:00</t>
+    <t>2024-12-03T09:13:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-MedicationRequest.xlsx
+++ b/StructureDefinition-MedicationRequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-03T09:13:19+00:00</t>
+    <t>2024-12-03T10:04:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-MedicationRequest.xlsx
+++ b/StructureDefinition-MedicationRequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-03T10:04:50+00:00</t>
+    <t>2024-12-05T14:20:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-MedicationRequest.xlsx
+++ b/StructureDefinition-MedicationRequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-05T14:20:46+00:00</t>
+    <t>2024-12-10T07:51:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-MedicationRequest.xlsx
+++ b/StructureDefinition-MedicationRequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-10T07:51:08+00:00</t>
+    <t>2024-12-10T08:19:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-MedicationRequest.xlsx
+++ b/StructureDefinition-MedicationRequest.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.9.0</t>
+    <t>1.10.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-10T08:19:29+00:00</t>
+    <t>2024-12-10T08:34:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-MedicationRequest.xlsx
+++ b/StructureDefinition-MedicationRequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-10T08:34:20+00:00</t>
+    <t>2024-12-10T08:45:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-MedicationRequest.xlsx
+++ b/StructureDefinition-MedicationRequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-10T08:45:26+00:00</t>
+    <t>2024-12-18T07:23:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-MedicationRequest.xlsx
+++ b/StructureDefinition-MedicationRequest.xlsx
@@ -27,7 +27,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://hl7.nl/fhir/zorgviewer/StructureDefinition/MedicationRequest</t>
+    <t>http://fhir.hl7.nl/zorgviewer/StructureDefinition/MedicationRequest</t>
   </si>
   <si>
     <t>Version</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-18T07:23:17+00:00</t>
+    <t>2024-12-23T09:34:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-MedicationRequest.xlsx
+++ b/StructureDefinition-MedicationRequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-23T09:34:32+00:00</t>
+    <t>2024-12-23T15:35:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-MedicationRequest.xlsx
+++ b/StructureDefinition-MedicationRequest.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5350" uniqueCount="811">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5350" uniqueCount="804">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-23T15:35:28+00:00</t>
+    <t>2024-12-27T09:44:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1756,25 +1756,17 @@
     <t>MedicationRequest.dosageInstruction</t>
   </si>
   <si>
-    <t xml:space="preserve">Gebruiksinstructie
-</t>
-  </si>
-  <si>
     <t xml:space="preserve">Dosage {http://nictiz.nl/fhir/StructureDefinition/zib-InstructionsForUse}
 </t>
   </si>
   <si>
-    <t>InstructionsForUse</t>
+    <t>How the medication should be taken</t>
   </si>
   <si>
     <t>Instructions for the use of the medication, e.g. dose and route of administration</t>
   </si>
   <si>
-    <t>The wiki page https://informatiestandaarden.nictiz.nl/wiki/mp:V9.0_Voorbeelden_doseringen provides dosage instruction examples. These examples consists of functional data and their representation in FHIR and CDA.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() | (children().count() &gt; id.count())}
-</t>
+    <t>There are examples where a medication request may include the option of an oral dose or an Intravenous or Intramuscular dose.  For example, "Ondansetron 8mg orally or IV twice a day as needed for nausea" or "Compazine® (prochlorperazine) 5-10mg PO or 25mg PR bid prn nausea or vomiting".  In these cases, two medication requests would be created that could be grouped together.  The decision on which dose and route of administration to use is based on the patient's condition at the time the dose is needed.</t>
   </si>
   <si>
     <t>NL-CM:9.6.23240</t>
@@ -1783,7 +1775,10 @@
     <t>NL-CM:0.0.14</t>
   </si>
   <si>
-    <t>.outboundRelationship[typeCode=COMP].target[classCode=SBADM, moodCode=INT]</t>
+    <t>…occurrence[x]</t>
+  </si>
+  <si>
+    <t>see dosageInstruction mapping</t>
   </si>
   <si>
     <t>MedicationRequest.dosageInstruction.id</t>
@@ -1871,21 +1866,17 @@
     <t>MedicationRequest.dosageInstruction.timing</t>
   </si>
   <si>
-    <t xml:space="preserve">Toedieningsschema
-</t>
-  </si>
-  <si>
     <t xml:space="preserve">Timing {http://nictiz.nl/fhir/StructureDefinition/zib-AdministrationSchedule}
 </t>
   </si>
   <si>
-    <t>AdministeringSchedule</t>
+    <t>When medication should be administered</t>
   </si>
   <si>
     <t>Specifications of the times at which the medication is to be administered. This is indicated as follows:                  Time(s) (16:00) or indications (“before meals”) at which the medication is to be taken each day.                 A specific number of times the medication is to be taken each day (“3x a day“), indicated with the frequency                 A time interval between consecutive doses (“Every 2 hours”, “every 3 days”), indicated with the word Interval.                 Combined periods with an interval and duration (“1 daily for three out of four weeks: the pill schedule”)                                                   If a certain medication is not to be taken daily, the aforementioned can be combined with daily indications:                  One or more week days on which the medication is to be administered (e.g. “Monday, Wednesday, Friday”)                 ”3x a week”, “2x a month”.                                                   The specified administration “infinite” is automatically to be repeated until:                  The end date and time has been reached                 The total administration duration has been reached (14 days)                                                   A specific amount of administrations has been reached (“20 doses”, “one-time only”), to be entered in the NumberOfDoses concept.</t>
   </si>
   <si>
-    <t>A timing schedule can be either a list of events - intervals on which the event occurs, or a single event with repeating criteria or just repeating criteria with no actual event.  When both event and a repeating specification are provided, the list of events should be understood as an interpretation of the information in the repeat structure.</t>
+    <t>This attribute may not always be populated while the Dosage.text is expected to be populated.  If both are populated, then the Dosage.text should reflect the content of the Dosage.timing.</t>
   </si>
   <si>
     <t>The timing schedule for giving the medication to the patient. The Schedule data type allows many different expressions. For example: "Every 8 hours"; "Three times a day"; "1/2 an hour before breakfast for 10 days from 23-Dec 2011:"; "15 Oct 2013, 17 Oct 2013 and 1 Nov 2013".  Sometimes, a rate can imply duration when expressed as total volume / duration (e.g.  500mL/2 hours implies a duration of 2 hours).  However, when rate doesn't imply duration (e.g. 250mL/hour), then the timing.repeat.duration is needed to convey the infuse over time period.</t>
@@ -1894,7 +1885,7 @@
     <t>Dosage.timing</t>
   </si>
   <si>
-    <t>QSET&lt;TS&gt; (GTS)</t>
+    <t>.effectiveTime</t>
   </si>
   <si>
     <t>MedicationRequest.dosageInstruction.asNeeded[x]</t>
@@ -2094,29 +2085,16 @@
 </t>
   </si>
   <si>
-    <t>A fixed quantity (no comparator)</t>
-  </si>
-  <si>
-    <t>The comparator is not used on a SimpleQuantity</t>
-  </si>
-  <si>
-    <t>The context of use may frequently define what kind of quantity this is and therefore what kind of units can be used. The context of use may also restrict the values for the comparator.</t>
+    <t>Amount of medication per dose</t>
+  </si>
+  <si>
+    <t>Amount of medication per dose.</t>
   </si>
   <si>
     <t>GstdTabel902</t>
   </si>
   <si>
     <t>http://decor.nictiz.nl/fhir/ValueSet/2.16.840.1.113883.2.4.3.11.60.20.77.11.27--20160830202453</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() | (children().count() &gt; id.count())}
-qty-3:If a code for the unit is present, the system SHALL also be present {code.empty() or system.exists()}sqty-1:The comparator is not used on a SimpleQuantity {comparator.empty()}</t>
-  </si>
-  <si>
-    <t>PQ, IVL&lt;PQ&gt;, MO, CO, depending on the values</t>
-  </si>
-  <si>
-    <t>SN (see also Range) or CQ</t>
   </si>
   <si>
     <t>MedicationRequest.dosageInstruction.dose[x]:doseRange</t>
@@ -2127,12 +2105,6 @@
   <si>
     <t xml:space="preserve">Range
 </t>
-  </si>
-  <si>
-    <t>Amount of medication per dose</t>
-  </si>
-  <si>
-    <t>Amount of medication per dose.</t>
   </si>
   <si>
     <t>MedicationRequest.dosageInstruction.dose[x]:doseRange.id</t>
@@ -2343,6 +2315,10 @@
   </si>
   <si>
     <t>Indicates the specific details for the dispense or medication supply part of a medication request (also known as a Medication Prescription or Medication Order).  Note that this information is not always sent with the order.  There may be in some settings (e.g. hospitals) institutional or system support for completing the dispense details in the pharmacy department.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() | (children().count() &gt; id.count())}
+</t>
   </si>
   <si>
     <t>Message/Body/NewRx/MedicationPrescribed/ExpirationDate</t>
@@ -13263,7 +13239,7 @@
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
-        <v>547</v>
+        <v>85</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
@@ -13282,16 +13258,16 @@
         <v>85</v>
       </c>
       <c r="K81" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="L81" t="s" s="2">
         <v>548</v>
       </c>
-      <c r="L81" t="s" s="2">
+      <c r="M81" t="s" s="2">
         <v>549</v>
       </c>
-      <c r="M81" t="s" s="2">
+      <c r="N81" t="s" s="2">
         <v>550</v>
-      </c>
-      <c r="N81" t="s" s="2">
-        <v>551</v>
       </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
@@ -13350,31 +13326,31 @@
         <v>84</v>
       </c>
       <c r="AI81" t="s" s="2">
-        <v>153</v>
+        <v>85</v>
       </c>
       <c r="AJ81" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AK81" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="AL81" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AM81" t="s" s="2">
         <v>552</v>
       </c>
-      <c r="AK81" t="s" s="2">
+      <c r="AN81" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AO81" t="s" s="2">
         <v>553</v>
       </c>
-      <c r="AL81" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AM81" t="s" s="2">
+      <c r="AP81" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AQ81" t="s" s="2">
         <v>554</v>
-      </c>
-      <c r="AN81" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AO81" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AP81" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AQ81" t="s" s="2">
-        <v>555</v>
       </c>
       <c r="AR81" t="s" s="2">
         <v>85</v>
@@ -13385,10 +13361,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -13512,10 +13488,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -13641,14 +13617,14 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
@@ -13667,17 +13643,17 @@
         <v>96</v>
       </c>
       <c r="K84" t="s" s="2">
+        <v>559</v>
+      </c>
+      <c r="L84" t="s" s="2">
         <v>560</v>
       </c>
-      <c r="L84" t="s" s="2">
+      <c r="M84" t="s" s="2">
         <v>561</v>
-      </c>
-      <c r="M84" t="s" s="2">
-        <v>562</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" t="s" s="2">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>85</v>
@@ -13726,7 +13702,7 @@
         <v>85</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>83</v>
@@ -13759,7 +13735,7 @@
         <v>85</v>
       </c>
       <c r="AQ84" t="s" s="2">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="AR84" t="s" s="2">
         <v>85</v>
@@ -13770,14 +13746,14 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
@@ -13802,11 +13778,11 @@
         <v>21</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" t="s" s="2">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="P85" t="s" s="2">
         <v>85</v>
@@ -13855,7 +13831,7 @@
         <v>85</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>83</v>
@@ -13888,7 +13864,7 @@
         <v>85</v>
       </c>
       <c r="AQ85" t="s" s="2">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="AR85" t="s" s="2">
         <v>85</v>
@@ -13899,14 +13875,14 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="E86" s="2"/>
       <c r="F86" t="s" s="2">
@@ -13928,14 +13904,14 @@
         <v>194</v>
       </c>
       <c r="L86" t="s" s="2">
+        <v>572</v>
+      </c>
+      <c r="M86" t="s" s="2">
         <v>573</v>
-      </c>
-      <c r="M86" t="s" s="2">
-        <v>574</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" t="s" s="2">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>85</v>
@@ -13964,25 +13940,25 @@
       </c>
       <c r="Y86" s="2"/>
       <c r="Z86" t="s" s="2">
+        <v>575</v>
+      </c>
+      <c r="AA86" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB86" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AC86" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AD86" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AE86" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AF86" t="s" s="2">
         <v>576</v>
-      </c>
-      <c r="AA86" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AB86" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AC86" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AD86" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AE86" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AF86" t="s" s="2">
-        <v>577</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>83</v>
@@ -14015,7 +13991,7 @@
         <v>85</v>
       </c>
       <c r="AQ86" t="s" s="2">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="AR86" t="s" s="2">
         <v>85</v>
@@ -14026,10 +14002,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -14055,10 +14031,10 @@
         <v>172</v>
       </c>
       <c r="L87" t="s" s="2">
+        <v>578</v>
+      </c>
+      <c r="M87" t="s" s="2">
         <v>579</v>
-      </c>
-      <c r="M87" t="s" s="2">
-        <v>580</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
@@ -14109,7 +14085,7 @@
         <v>85</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>83</v>
@@ -14142,7 +14118,7 @@
         <v>85</v>
       </c>
       <c r="AQ87" t="s" s="2">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="AR87" t="s" s="2">
         <v>85</v>
@@ -14153,14 +14129,14 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
-        <v>583</v>
+        <v>85</v>
       </c>
       <c r="E88" s="2"/>
       <c r="F88" t="s" s="2">
@@ -14176,22 +14152,22 @@
         <v>85</v>
       </c>
       <c r="J88" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K88" t="s" s="2">
+        <v>582</v>
+      </c>
+      <c r="L88" t="s" s="2">
+        <v>583</v>
+      </c>
+      <c r="M88" t="s" s="2">
         <v>584</v>
       </c>
-      <c r="L88" t="s" s="2">
+      <c r="N88" t="s" s="2">
         <v>585</v>
       </c>
-      <c r="M88" t="s" s="2">
+      <c r="O88" t="s" s="2">
         <v>586</v>
-      </c>
-      <c r="N88" t="s" s="2">
-        <v>587</v>
-      </c>
-      <c r="O88" t="s" s="2">
-        <v>588</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>85</v>
@@ -14240,7 +14216,7 @@
         <v>85</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>83</v>
@@ -14249,10 +14225,10 @@
         <v>95</v>
       </c>
       <c r="AI88" t="s" s="2">
-        <v>153</v>
+        <v>85</v>
       </c>
       <c r="AJ88" t="s" s="2">
-        <v>552</v>
+        <v>85</v>
       </c>
       <c r="AK88" t="s" s="2">
         <v>85</v>
@@ -14273,21 +14249,21 @@
         <v>85</v>
       </c>
       <c r="AQ88" t="s" s="2">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="AR88" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS88" t="s" s="2">
-        <v>138</v>
+        <v>85</v>
       </c>
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -14313,13 +14289,13 @@
         <v>194</v>
       </c>
       <c r="L89" t="s" s="2">
+        <v>590</v>
+      </c>
+      <c r="M89" t="s" s="2">
+        <v>591</v>
+      </c>
+      <c r="N89" t="s" s="2">
         <v>592</v>
-      </c>
-      <c r="M89" t="s" s="2">
-        <v>593</v>
-      </c>
-      <c r="N89" t="s" s="2">
-        <v>594</v>
       </c>
       <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
@@ -14345,13 +14321,13 @@
         <v>85</v>
       </c>
       <c r="X89" t="s" s="2">
+        <v>593</v>
+      </c>
+      <c r="Y89" t="s" s="2">
+        <v>594</v>
+      </c>
+      <c r="Z89" t="s" s="2">
         <v>595</v>
-      </c>
-      <c r="Y89" t="s" s="2">
-        <v>596</v>
-      </c>
-      <c r="Z89" t="s" s="2">
-        <v>597</v>
       </c>
       <c r="AA89" t="s" s="2">
         <v>85</v>
@@ -14367,7 +14343,7 @@
         <v>198</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>83</v>
@@ -14400,7 +14376,7 @@
         <v>85</v>
       </c>
       <c r="AQ89" t="s" s="2">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="AR89" t="s" s="2">
         <v>85</v>
@@ -14411,16 +14387,16 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
+        <v>598</v>
+      </c>
+      <c r="B90" t="s" s="2">
+        <v>589</v>
+      </c>
+      <c r="C90" t="s" s="2">
+        <v>599</v>
+      </c>
+      <c r="D90" t="s" s="2">
         <v>600</v>
-      </c>
-      <c r="B90" t="s" s="2">
-        <v>591</v>
-      </c>
-      <c r="C90" t="s" s="2">
-        <v>601</v>
-      </c>
-      <c r="D90" t="s" s="2">
-        <v>602</v>
       </c>
       <c r="E90" s="2"/>
       <c r="F90" t="s" s="2">
@@ -14442,13 +14418,13 @@
         <v>194</v>
       </c>
       <c r="L90" t="s" s="2">
+        <v>601</v>
+      </c>
+      <c r="M90" t="s" s="2">
+        <v>602</v>
+      </c>
+      <c r="N90" t="s" s="2">
         <v>603</v>
-      </c>
-      <c r="M90" t="s" s="2">
-        <v>604</v>
-      </c>
-      <c r="N90" t="s" s="2">
-        <v>605</v>
       </c>
       <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
@@ -14477,10 +14453,10 @@
         <v>118</v>
       </c>
       <c r="Y90" t="s" s="2">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="Z90" t="s" s="2">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="AA90" t="s" s="2">
         <v>85</v>
@@ -14498,7 +14474,7 @@
         <v>85</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>83</v>
@@ -14531,7 +14507,7 @@
         <v>85</v>
       </c>
       <c r="AQ90" t="s" s="2">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="AR90" t="s" s="2">
         <v>85</v>
@@ -14542,10 +14518,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -14571,16 +14547,16 @@
         <v>194</v>
       </c>
       <c r="L91" t="s" s="2">
+        <v>607</v>
+      </c>
+      <c r="M91" t="s" s="2">
+        <v>608</v>
+      </c>
+      <c r="N91" t="s" s="2">
         <v>609</v>
       </c>
-      <c r="M91" t="s" s="2">
+      <c r="O91" t="s" s="2">
         <v>610</v>
-      </c>
-      <c r="N91" t="s" s="2">
-        <v>611</v>
-      </c>
-      <c r="O91" t="s" s="2">
-        <v>612</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>85</v>
@@ -14605,31 +14581,31 @@
         <v>85</v>
       </c>
       <c r="X91" t="s" s="2">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="Y91" t="s" s="2">
+        <v>611</v>
+      </c>
+      <c r="Z91" t="s" s="2">
+        <v>612</v>
+      </c>
+      <c r="AA91" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB91" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AC91" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AD91" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AE91" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AF91" t="s" s="2">
         <v>613</v>
-      </c>
-      <c r="Z91" t="s" s="2">
-        <v>614</v>
-      </c>
-      <c r="AA91" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AB91" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AC91" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AD91" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AE91" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AF91" t="s" s="2">
-        <v>615</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>83</v>
@@ -14662,7 +14638,7 @@
         <v>85</v>
       </c>
       <c r="AQ91" t="s" s="2">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="AR91" t="s" s="2">
         <v>85</v>
@@ -14673,14 +14649,14 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="E92" s="2"/>
       <c r="F92" t="s" s="2">
@@ -14702,14 +14678,14 @@
         <v>194</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="N92" s="2"/>
       <c r="O92" t="s" s="2">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>85</v>
@@ -14722,7 +14698,7 @@
         <v>85</v>
       </c>
       <c r="T92" t="s" s="2">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="U92" t="s" s="2">
         <v>85</v>
@@ -14737,28 +14713,28 @@
         <v>118</v>
       </c>
       <c r="Y92" t="s" s="2">
+        <v>621</v>
+      </c>
+      <c r="Z92" t="s" s="2">
+        <v>622</v>
+      </c>
+      <c r="AA92" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB92" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AC92" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AD92" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AE92" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AF92" t="s" s="2">
         <v>623</v>
-      </c>
-      <c r="Z92" t="s" s="2">
-        <v>624</v>
-      </c>
-      <c r="AA92" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AB92" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AC92" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AD92" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AE92" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AF92" t="s" s="2">
-        <v>625</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>83</v>
@@ -14791,7 +14767,7 @@
         <v>85</v>
       </c>
       <c r="AQ92" t="s" s="2">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="AR92" t="s" s="2">
         <v>85</v>
@@ -14802,10 +14778,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -14929,10 +14905,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -15058,10 +15034,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -15189,10 +15165,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -15320,10 +15296,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -15349,16 +15325,16 @@
         <v>194</v>
       </c>
       <c r="L97" t="s" s="2">
+        <v>630</v>
+      </c>
+      <c r="M97" t="s" s="2">
+        <v>631</v>
+      </c>
+      <c r="N97" t="s" s="2">
         <v>632</v>
       </c>
-      <c r="M97" t="s" s="2">
+      <c r="O97" t="s" s="2">
         <v>633</v>
-      </c>
-      <c r="N97" t="s" s="2">
-        <v>634</v>
-      </c>
-      <c r="O97" t="s" s="2">
-        <v>635</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>85</v>
@@ -15383,31 +15359,31 @@
         <v>85</v>
       </c>
       <c r="X97" t="s" s="2">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="Y97" t="s" s="2">
+        <v>634</v>
+      </c>
+      <c r="Z97" t="s" s="2">
+        <v>635</v>
+      </c>
+      <c r="AA97" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB97" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AC97" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AD97" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AE97" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AF97" t="s" s="2">
         <v>636</v>
-      </c>
-      <c r="Z97" t="s" s="2">
-        <v>637</v>
-      </c>
-      <c r="AA97" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AB97" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AC97" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AD97" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AE97" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AF97" t="s" s="2">
-        <v>638</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>83</v>
@@ -15440,7 +15416,7 @@
         <v>85</v>
       </c>
       <c r="AQ97" t="s" s="2">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="AR97" t="s" s="2">
         <v>85</v>
@@ -15451,14 +15427,14 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="E98" s="2"/>
       <c r="F98" t="s" s="2">
@@ -15477,19 +15453,19 @@
         <v>96</v>
       </c>
       <c r="K98" t="s" s="2">
+        <v>640</v>
+      </c>
+      <c r="L98" t="s" s="2">
+        <v>641</v>
+      </c>
+      <c r="M98" t="s" s="2">
         <v>642</v>
       </c>
-      <c r="L98" t="s" s="2">
+      <c r="N98" t="s" s="2">
         <v>643</v>
       </c>
-      <c r="M98" t="s" s="2">
+      <c r="O98" t="s" s="2">
         <v>644</v>
-      </c>
-      <c r="N98" t="s" s="2">
-        <v>645</v>
-      </c>
-      <c r="O98" t="s" s="2">
-        <v>646</v>
       </c>
       <c r="P98" t="s" s="2">
         <v>85</v>
@@ -15536,7 +15512,7 @@
         <v>198</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>83</v>
@@ -15569,7 +15545,7 @@
         <v>85</v>
       </c>
       <c r="AQ98" t="s" s="2">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="AR98" t="s" s="2">
         <v>85</v>
@@ -15580,13 +15556,13 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="C99" t="s" s="2">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="D99" t="s" s="2">
         <v>85</v>
@@ -15605,22 +15581,22 @@
         <v>85</v>
       </c>
       <c r="J99" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K99" t="s" s="2">
+        <v>648</v>
+      </c>
+      <c r="L99" t="s" s="2">
+        <v>649</v>
+      </c>
+      <c r="M99" t="s" s="2">
         <v>650</v>
       </c>
-      <c r="L99" t="s" s="2">
-        <v>651</v>
-      </c>
-      <c r="M99" t="s" s="2">
-        <v>652</v>
-      </c>
       <c r="N99" t="s" s="2">
-        <v>653</v>
+        <v>643</v>
       </c>
       <c r="O99" t="s" s="2">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="P99" t="s" s="2">
         <v>85</v>
@@ -15648,10 +15624,10 @@
         <v>238</v>
       </c>
       <c r="Y99" t="s" s="2">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="Z99" t="s" s="2">
-        <v>655</v>
+        <v>652</v>
       </c>
       <c r="AA99" t="s" s="2">
         <v>85</v>
@@ -15669,7 +15645,7 @@
         <v>85</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>83</v>
@@ -15678,10 +15654,10 @@
         <v>95</v>
       </c>
       <c r="AI99" t="s" s="2">
-        <v>153</v>
+        <v>85</v>
       </c>
       <c r="AJ99" t="s" s="2">
-        <v>656</v>
+        <v>85</v>
       </c>
       <c r="AK99" t="s" s="2">
         <v>85</v>
@@ -15702,24 +15678,24 @@
         <v>85</v>
       </c>
       <c r="AQ99" t="s" s="2">
-        <v>657</v>
+        <v>637</v>
       </c>
       <c r="AR99" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS99" t="s" s="2">
-        <v>658</v>
+        <v>85</v>
       </c>
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>659</v>
+        <v>653</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="C100" t="s" s="2">
-        <v>660</v>
+        <v>654</v>
       </c>
       <c r="D100" t="s" s="2">
         <v>85</v>
@@ -15741,19 +15717,19 @@
         <v>96</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>661</v>
+        <v>655</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>662</v>
+        <v>649</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>663</v>
+        <v>650</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="O100" t="s" s="2">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>85</v>
@@ -15802,7 +15778,7 @@
         <v>85</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>83</v>
@@ -15835,7 +15811,7 @@
         <v>85</v>
       </c>
       <c r="AQ100" t="s" s="2">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="AR100" t="s" s="2">
         <v>85</v>
@@ -15846,10 +15822,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>664</v>
+        <v>656</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>665</v>
+        <v>657</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -15973,10 +15949,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>666</v>
+        <v>658</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>667</v>
+        <v>659</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -16102,10 +16078,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>668</v>
+        <v>660</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>669</v>
+        <v>661</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -16128,16 +16104,16 @@
         <v>96</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>670</v>
+        <v>662</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>671</v>
+        <v>663</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>672</v>
+        <v>664</v>
       </c>
       <c r="O103" s="2"/>
       <c r="P103" t="s" s="2">
@@ -16166,10 +16142,10 @@
         <v>238</v>
       </c>
       <c r="Y103" t="s" s="2">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="Z103" t="s" s="2">
-        <v>655</v>
+        <v>652</v>
       </c>
       <c r="AA103" t="s" s="2">
         <v>85</v>
@@ -16187,7 +16163,7 @@
         <v>85</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>673</v>
+        <v>665</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>83</v>
@@ -16196,7 +16172,7 @@
         <v>95</v>
       </c>
       <c r="AI103" t="s" s="2">
-        <v>674</v>
+        <v>666</v>
       </c>
       <c r="AJ103" t="s" s="2">
         <v>85</v>
@@ -16220,21 +16196,21 @@
         <v>85</v>
       </c>
       <c r="AQ103" t="s" s="2">
-        <v>675</v>
+        <v>667</v>
       </c>
       <c r="AR103" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS103" t="s" s="2">
-        <v>676</v>
+        <v>668</v>
       </c>
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>677</v>
+        <v>669</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>678</v>
+        <v>670</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -16257,16 +16233,16 @@
         <v>96</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>679</v>
+        <v>671</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>680</v>
+        <v>672</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>681</v>
+        <v>673</v>
       </c>
       <c r="O104" s="2"/>
       <c r="P104" t="s" s="2">
@@ -16295,10 +16271,10 @@
         <v>238</v>
       </c>
       <c r="Y104" t="s" s="2">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="Z104" t="s" s="2">
-        <v>655</v>
+        <v>652</v>
       </c>
       <c r="AA104" t="s" s="2">
         <v>85</v>
@@ -16316,7 +16292,7 @@
         <v>85</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>682</v>
+        <v>674</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>83</v>
@@ -16325,7 +16301,7 @@
         <v>95</v>
       </c>
       <c r="AI104" t="s" s="2">
-        <v>674</v>
+        <v>666</v>
       </c>
       <c r="AJ104" t="s" s="2">
         <v>85</v>
@@ -16349,25 +16325,25 @@
         <v>85</v>
       </c>
       <c r="AQ104" t="s" s="2">
-        <v>683</v>
+        <v>675</v>
       </c>
       <c r="AR104" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS104" t="s" s="2">
-        <v>684</v>
+        <v>676</v>
       </c>
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>685</v>
+        <v>677</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>685</v>
+        <v>677</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
-        <v>686</v>
+        <v>678</v>
       </c>
       <c r="E105" s="2"/>
       <c r="F105" t="s" s="2">
@@ -16386,19 +16362,19 @@
         <v>96</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>687</v>
+        <v>679</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>688</v>
+        <v>680</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>689</v>
+        <v>681</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>690</v>
+        <v>682</v>
       </c>
       <c r="O105" t="s" s="2">
-        <v>691</v>
+        <v>683</v>
       </c>
       <c r="P105" t="s" s="2">
         <v>85</v>
@@ -16447,7 +16423,7 @@
         <v>85</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>692</v>
+        <v>684</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>83</v>
@@ -16480,7 +16456,7 @@
         <v>85</v>
       </c>
       <c r="AQ105" t="s" s="2">
-        <v>693</v>
+        <v>685</v>
       </c>
       <c r="AR105" t="s" s="2">
         <v>85</v>
@@ -16491,10 +16467,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>694</v>
+        <v>686</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>694</v>
+        <v>686</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -16618,10 +16594,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>695</v>
+        <v>687</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>695</v>
+        <v>687</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -16747,10 +16723,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>696</v>
+        <v>688</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>696</v>
+        <v>688</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -16773,13 +16749,13 @@
         <v>96</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>697</v>
+        <v>689</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>698</v>
+        <v>690</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>699</v>
+        <v>691</v>
       </c>
       <c r="N108" s="2"/>
       <c r="O108" s="2"/>
@@ -16809,10 +16785,10 @@
         <v>238</v>
       </c>
       <c r="Y108" t="s" s="2">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="Z108" t="s" s="2">
-        <v>655</v>
+        <v>652</v>
       </c>
       <c r="AA108" t="s" s="2">
         <v>85</v>
@@ -16830,7 +16806,7 @@
         <v>85</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>700</v>
+        <v>692</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>83</v>
@@ -16863,7 +16839,7 @@
         <v>85</v>
       </c>
       <c r="AQ108" t="s" s="2">
-        <v>701</v>
+        <v>693</v>
       </c>
       <c r="AR108" t="s" s="2">
         <v>85</v>
@@ -16874,10 +16850,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>702</v>
+        <v>694</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>702</v>
+        <v>694</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -16900,13 +16876,13 @@
         <v>96</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>697</v>
+        <v>689</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>703</v>
+        <v>695</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>704</v>
+        <v>696</v>
       </c>
       <c r="N109" s="2"/>
       <c r="O109" s="2"/>
@@ -16957,7 +16933,7 @@
         <v>85</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>705</v>
+        <v>697</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>83</v>
@@ -16990,7 +16966,7 @@
         <v>85</v>
       </c>
       <c r="AQ109" t="s" s="2">
-        <v>706</v>
+        <v>698</v>
       </c>
       <c r="AR109" t="s" s="2">
         <v>85</v>
@@ -17001,10 +16977,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>707</v>
+        <v>699</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>707</v>
+        <v>699</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -17027,19 +17003,19 @@
         <v>96</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>708</v>
+        <v>700</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>709</v>
+        <v>701</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>710</v>
+        <v>702</v>
       </c>
       <c r="O110" t="s" s="2">
-        <v>711</v>
+        <v>703</v>
       </c>
       <c r="P110" t="s" s="2">
         <v>85</v>
@@ -17088,7 +17064,7 @@
         <v>85</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>712</v>
+        <v>704</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>83</v>
@@ -17121,7 +17097,7 @@
         <v>85</v>
       </c>
       <c r="AQ110" t="s" s="2">
-        <v>713</v>
+        <v>705</v>
       </c>
       <c r="AR110" t="s" s="2">
         <v>85</v>
@@ -17132,10 +17108,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>714</v>
+        <v>706</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>714</v>
+        <v>706</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -17158,17 +17134,17 @@
         <v>96</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>715</v>
+        <v>707</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>716</v>
+        <v>708</v>
       </c>
       <c r="N111" s="2"/>
       <c r="O111" t="s" s="2">
-        <v>717</v>
+        <v>709</v>
       </c>
       <c r="P111" t="s" s="2">
         <v>85</v>
@@ -17217,7 +17193,7 @@
         <v>85</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>718</v>
+        <v>710</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>83</v>
@@ -17250,7 +17226,7 @@
         <v>85</v>
       </c>
       <c r="AQ111" t="s" s="2">
-        <v>713</v>
+        <v>705</v>
       </c>
       <c r="AR111" t="s" s="2">
         <v>85</v>
@@ -17261,14 +17237,14 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>719</v>
+        <v>711</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>719</v>
+        <v>711</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
-        <v>720</v>
+        <v>712</v>
       </c>
       <c r="E112" s="2"/>
       <c r="F112" t="s" s="2">
@@ -17287,19 +17263,19 @@
         <v>96</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>721</v>
+        <v>713</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>722</v>
+        <v>714</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>723</v>
+        <v>715</v>
       </c>
       <c r="N112" t="s" s="2">
-        <v>724</v>
+        <v>716</v>
       </c>
       <c r="O112" t="s" s="2">
-        <v>725</v>
+        <v>717</v>
       </c>
       <c r="P112" t="s" s="2">
         <v>85</v>
@@ -17348,7 +17324,7 @@
         <v>85</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>726</v>
+        <v>718</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>83</v>
@@ -17381,7 +17357,7 @@
         <v>85</v>
       </c>
       <c r="AQ112" t="s" s="2">
-        <v>727</v>
+        <v>719</v>
       </c>
       <c r="AR112" t="s" s="2">
         <v>85</v>
@@ -17392,10 +17368,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>728</v>
+        <v>720</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>728</v>
+        <v>720</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -17421,10 +17397,10 @@
         <v>462</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>729</v>
+        <v>721</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>730</v>
+        <v>722</v>
       </c>
       <c r="N113" s="2"/>
       <c r="O113" s="2"/>
@@ -17475,7 +17451,7 @@
         <v>85</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>728</v>
+        <v>720</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>83</v>
@@ -17487,7 +17463,7 @@
         <v>85</v>
       </c>
       <c r="AJ113" t="s" s="2">
-        <v>552</v>
+        <v>723</v>
       </c>
       <c r="AK113" t="s" s="2">
         <v>85</v>
@@ -17505,10 +17481,10 @@
         <v>85</v>
       </c>
       <c r="AP113" t="s" s="2">
-        <v>731</v>
+        <v>724</v>
       </c>
       <c r="AQ113" t="s" s="2">
-        <v>732</v>
+        <v>725</v>
       </c>
       <c r="AR113" t="s" s="2">
         <v>85</v>
@@ -17519,10 +17495,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>733</v>
+        <v>726</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>733</v>
+        <v>726</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -17646,10 +17622,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>734</v>
+        <v>727</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>734</v>
+        <v>727</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -17775,10 +17751,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>735</v>
+        <v>728</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>735</v>
+        <v>728</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -17904,10 +17880,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>736</v>
+        <v>729</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>736</v>
+        <v>729</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -17930,19 +17906,19 @@
         <v>85</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>737</v>
+        <v>730</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>738</v>
+        <v>731</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>739</v>
+        <v>732</v>
       </c>
       <c r="N117" t="s" s="2">
-        <v>740</v>
+        <v>733</v>
       </c>
       <c r="O117" t="s" s="2">
-        <v>741</v>
+        <v>734</v>
       </c>
       <c r="P117" t="s" s="2">
         <v>85</v>
@@ -17991,7 +17967,7 @@
         <v>85</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>736</v>
+        <v>729</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>83</v>
@@ -18021,10 +17997,10 @@
         <v>85</v>
       </c>
       <c r="AP117" t="s" s="2">
-        <v>742</v>
+        <v>735</v>
       </c>
       <c r="AQ117" t="s" s="2">
-        <v>743</v>
+        <v>736</v>
       </c>
       <c r="AR117" t="s" s="2">
         <v>85</v>
@@ -18035,10 +18011,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>744</v>
+        <v>737</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>744</v>
+        <v>737</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -18061,16 +18037,16 @@
         <v>85</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>745</v>
+        <v>738</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>746</v>
+        <v>739</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>747</v>
+        <v>740</v>
       </c>
       <c r="N118" t="s" s="2">
-        <v>748</v>
+        <v>741</v>
       </c>
       <c r="O118" s="2"/>
       <c r="P118" t="s" s="2">
@@ -18120,7 +18096,7 @@
         <v>85</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>744</v>
+        <v>737</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>83</v>
@@ -18150,24 +18126,24 @@
         <v>85</v>
       </c>
       <c r="AP118" t="s" s="2">
-        <v>749</v>
+        <v>742</v>
       </c>
       <c r="AQ118" t="s" s="2">
-        <v>750</v>
+        <v>743</v>
       </c>
       <c r="AR118" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS118" t="s" s="2">
-        <v>751</v>
+        <v>744</v>
       </c>
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>752</v>
+        <v>745</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>752</v>
+        <v>745</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -18190,13 +18166,13 @@
         <v>85</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>753</v>
+        <v>746</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>754</v>
+        <v>747</v>
       </c>
       <c r="N119" s="2"/>
       <c r="O119" s="2"/>
@@ -18247,7 +18223,7 @@
         <v>85</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>752</v>
+        <v>745</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>83</v>
@@ -18277,24 +18253,24 @@
         <v>85</v>
       </c>
       <c r="AP119" t="s" s="2">
-        <v>755</v>
+        <v>748</v>
       </c>
       <c r="AQ119" t="s" s="2">
-        <v>756</v>
+        <v>749</v>
       </c>
       <c r="AR119" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS119" t="s" s="2">
-        <v>757</v>
+        <v>750</v>
       </c>
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>758</v>
+        <v>751</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>758</v>
+        <v>751</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -18317,16 +18293,16 @@
         <v>85</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>759</v>
+        <v>752</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>760</v>
+        <v>753</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>761</v>
+        <v>754</v>
       </c>
       <c r="N120" t="s" s="2">
-        <v>762</v>
+        <v>755</v>
       </c>
       <c r="O120" s="2"/>
       <c r="P120" t="s" s="2">
@@ -18376,7 +18352,7 @@
         <v>85</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>758</v>
+        <v>751</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>83</v>
@@ -18406,10 +18382,10 @@
         <v>85</v>
       </c>
       <c r="AP120" t="s" s="2">
-        <v>763</v>
+        <v>756</v>
       </c>
       <c r="AQ120" t="s" s="2">
-        <v>764</v>
+        <v>757</v>
       </c>
       <c r="AR120" t="s" s="2">
         <v>85</v>
@@ -18420,10 +18396,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>765</v>
+        <v>758</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>765</v>
+        <v>758</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -18446,13 +18422,13 @@
         <v>85</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>766</v>
+        <v>759</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>767</v>
+        <v>760</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>768</v>
+        <v>761</v>
       </c>
       <c r="N121" s="2"/>
       <c r="O121" s="2"/>
@@ -18503,7 +18479,7 @@
         <v>85</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>765</v>
+        <v>758</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>83</v>
@@ -18536,7 +18512,7 @@
         <v>85</v>
       </c>
       <c r="AQ121" t="s" s="2">
-        <v>769</v>
+        <v>762</v>
       </c>
       <c r="AR121" t="s" s="2">
         <v>508</v>
@@ -18547,10 +18523,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>770</v>
+        <v>763</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>770</v>
+        <v>763</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -18576,10 +18552,10 @@
         <v>462</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>771</v>
+        <v>764</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>772</v>
+        <v>765</v>
       </c>
       <c r="N122" s="2"/>
       <c r="O122" s="2"/>
@@ -18630,7 +18606,7 @@
         <v>85</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>770</v>
+        <v>763</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>83</v>
@@ -18642,7 +18618,7 @@
         <v>85</v>
       </c>
       <c r="AJ122" t="s" s="2">
-        <v>552</v>
+        <v>723</v>
       </c>
       <c r="AK122" t="s" s="2">
         <v>85</v>
@@ -18660,10 +18636,10 @@
         <v>85</v>
       </c>
       <c r="AP122" t="s" s="2">
-        <v>773</v>
+        <v>766</v>
       </c>
       <c r="AQ122" t="s" s="2">
-        <v>774</v>
+        <v>767</v>
       </c>
       <c r="AR122" t="s" s="2">
         <v>85</v>
@@ -18674,10 +18650,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>775</v>
+        <v>768</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>775</v>
+        <v>768</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -18801,10 +18777,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -18930,10 +18906,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>777</v>
+        <v>770</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>777</v>
+        <v>770</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -19059,10 +19035,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>778</v>
+        <v>771</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>778</v>
+        <v>771</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -19088,13 +19064,13 @@
         <v>360</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>779</v>
+        <v>772</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>780</v>
+        <v>773</v>
       </c>
       <c r="N126" t="s" s="2">
-        <v>781</v>
+        <v>774</v>
       </c>
       <c r="O126" s="2"/>
       <c r="P126" t="s" s="2">
@@ -19144,7 +19120,7 @@
         <v>85</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>778</v>
+        <v>771</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>95</v>
@@ -19174,24 +19150,24 @@
         <v>85</v>
       </c>
       <c r="AP126" t="s" s="2">
-        <v>773</v>
+        <v>766</v>
       </c>
       <c r="AQ126" t="s" s="2">
-        <v>782</v>
+        <v>775</v>
       </c>
       <c r="AR126" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS126" t="s" s="2">
-        <v>783</v>
+        <v>776</v>
       </c>
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>784</v>
+        <v>777</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>784</v>
+        <v>777</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -19217,10 +19193,10 @@
         <v>194</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>785</v>
+        <v>778</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>786</v>
+        <v>779</v>
       </c>
       <c r="N127" s="2"/>
       <c r="O127" s="2"/>
@@ -19247,13 +19223,13 @@
         <v>85</v>
       </c>
       <c r="X127" t="s" s="2">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="Y127" t="s" s="2">
-        <v>787</v>
+        <v>780</v>
       </c>
       <c r="Z127" t="s" s="2">
-        <v>788</v>
+        <v>781</v>
       </c>
       <c r="AA127" t="s" s="2">
         <v>85</v>
@@ -19271,7 +19247,7 @@
         <v>85</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>784</v>
+        <v>777</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>83</v>
@@ -19301,24 +19277,24 @@
         <v>85</v>
       </c>
       <c r="AP127" t="s" s="2">
-        <v>789</v>
+        <v>782</v>
       </c>
       <c r="AQ127" t="s" s="2">
-        <v>790</v>
+        <v>783</v>
       </c>
       <c r="AR127" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS127" t="s" s="2">
-        <v>791</v>
+        <v>784</v>
       </c>
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>792</v>
+        <v>785</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>792</v>
+        <v>785</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -19341,13 +19317,13 @@
         <v>85</v>
       </c>
       <c r="K128" t="s" s="2">
-        <v>793</v>
+        <v>786</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>794</v>
+        <v>787</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>795</v>
+        <v>788</v>
       </c>
       <c r="N128" s="2"/>
       <c r="O128" s="2"/>
@@ -19398,7 +19374,7 @@
         <v>85</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>792</v>
+        <v>785</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>83</v>
@@ -19425,13 +19401,13 @@
         <v>85</v>
       </c>
       <c r="AO128" t="s" s="2">
-        <v>796</v>
+        <v>789</v>
       </c>
       <c r="AP128" t="s" s="2">
-        <v>789</v>
+        <v>782</v>
       </c>
       <c r="AQ128" t="s" s="2">
-        <v>797</v>
+        <v>790</v>
       </c>
       <c r="AR128" t="s" s="2">
         <v>85</v>
@@ -19442,14 +19418,14 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>798</v>
+        <v>791</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>798</v>
+        <v>791</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
-        <v>799</v>
+        <v>792</v>
       </c>
       <c r="E129" s="2"/>
       <c r="F129" t="s" s="2">
@@ -19468,13 +19444,13 @@
         <v>85</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>800</v>
+        <v>793</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>801</v>
+        <v>794</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>802</v>
+        <v>795</v>
       </c>
       <c r="N129" s="2"/>
       <c r="O129" s="2"/>
@@ -19525,7 +19501,7 @@
         <v>85</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>798</v>
+        <v>791</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>83</v>
@@ -19558,7 +19534,7 @@
         <v>85</v>
       </c>
       <c r="AQ129" t="s" s="2">
-        <v>803</v>
+        <v>796</v>
       </c>
       <c r="AR129" t="s" s="2">
         <v>85</v>
@@ -19569,10 +19545,10 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>804</v>
+        <v>797</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>804</v>
+        <v>797</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -19595,16 +19571,16 @@
         <v>85</v>
       </c>
       <c r="K130" t="s" s="2">
-        <v>805</v>
+        <v>798</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>806</v>
+        <v>799</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>807</v>
+        <v>800</v>
       </c>
       <c r="N130" t="s" s="2">
-        <v>808</v>
+        <v>801</v>
       </c>
       <c r="O130" s="2"/>
       <c r="P130" t="s" s="2">
@@ -19654,7 +19630,7 @@
         <v>85</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>804</v>
+        <v>797</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>83</v>
@@ -19681,13 +19657,13 @@
         <v>85</v>
       </c>
       <c r="AO130" t="s" s="2">
-        <v>809</v>
+        <v>802</v>
       </c>
       <c r="AP130" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AQ130" t="s" s="2">
-        <v>810</v>
+        <v>803</v>
       </c>
       <c r="AR130" t="s" s="2">
         <v>85</v>

--- a/StructureDefinition-MedicationRequest.xlsx
+++ b/StructureDefinition-MedicationRequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-27T09:44:10+00:00</t>
+    <t>2024-12-27T09:59:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-MedicationRequest.xlsx
+++ b/StructureDefinition-MedicationRequest.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.10.0</t>
+    <t>1.11.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-27T09:59:08+00:00</t>
+    <t>2025-01-02T11:11:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-MedicationRequest.xlsx
+++ b/StructureDefinition-MedicationRequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-02T11:11:09+00:00</t>
+    <t>2025-01-02T12:37:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-MedicationRequest.xlsx
+++ b/StructureDefinition-MedicationRequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-02T12:37:15+00:00</t>
+    <t>2025-01-05T10:27:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-MedicationRequest.xlsx
+++ b/StructureDefinition-MedicationRequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-05T10:27:23+00:00</t>
+    <t>2025-01-05T10:53:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-MedicationRequest.xlsx
+++ b/StructureDefinition-MedicationRequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-05T10:53:29+00:00</t>
+    <t>2025-01-06T15:42:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-MedicationRequest.xlsx
+++ b/StructureDefinition-MedicationRequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-06T15:42:07+00:00</t>
+    <t>2025-01-06T15:50:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-MedicationRequest.xlsx
+++ b/StructureDefinition-MedicationRequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-06T15:50:28+00:00</t>
+    <t>2025-01-06T16:52:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-MedicationRequest.xlsx
+++ b/StructureDefinition-MedicationRequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-06T16:52:49+00:00</t>
+    <t>2025-01-06T17:00:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-MedicationRequest.xlsx
+++ b/StructureDefinition-MedicationRequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-06T17:00:55+00:00</t>
+    <t>2025-01-20T15:02:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-MedicationRequest.xlsx
+++ b/StructureDefinition-MedicationRequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-20T15:02:53+00:00</t>
+    <t>2025-01-28T20:06:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-MedicationRequest.xlsx
+++ b/StructureDefinition-MedicationRequest.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.11.0</t>
+    <t>1.12.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-28T20:06:40+00:00</t>
+    <t>2025-01-28T20:08:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-MedicationRequest.xlsx
+++ b/StructureDefinition-MedicationRequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-28T20:08:20+00:00</t>
+    <t>2025-01-28T20:50:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-MedicationRequest.xlsx
+++ b/StructureDefinition-MedicationRequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-28T20:50:34+00:00</t>
+    <t>2025-01-31T07:22:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-MedicationRequest.xlsx
+++ b/StructureDefinition-MedicationRequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-31T07:22:48+00:00</t>
+    <t>2025-01-31T13:40:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-MedicationRequest.xlsx
+++ b/StructureDefinition-MedicationRequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-31T13:40:12+00:00</t>
+    <t>2025-02-03T11:19:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-MedicationRequest.xlsx
+++ b/StructureDefinition-MedicationRequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-03T11:19:03+00:00</t>
+    <t>2025-02-03T16:53:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-MedicationRequest.xlsx
+++ b/StructureDefinition-MedicationRequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-03T16:53:34+00:00</t>
+    <t>2025-02-04T12:12:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-MedicationRequest.xlsx
+++ b/StructureDefinition-MedicationRequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-04T12:12:36+00:00</t>
+    <t>2025-02-05T13:44:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-MedicationRequest.xlsx
+++ b/StructureDefinition-MedicationRequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T13:44:35+00:00</t>
+    <t>2025-02-05T14:01:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-MedicationRequest.xlsx
+++ b/StructureDefinition-MedicationRequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T14:01:06+00:00</t>
+    <t>2025-02-05T14:12:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-MedicationRequest.xlsx
+++ b/StructureDefinition-MedicationRequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T14:12:35+00:00</t>
+    <t>2025-02-12T15:28:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-MedicationRequest.xlsx
+++ b/StructureDefinition-MedicationRequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-12T15:28:44+00:00</t>
+    <t>2025-02-13T13:25:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-MedicationRequest.xlsx
+++ b/StructureDefinition-MedicationRequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-13T13:25:12+00:00</t>
+    <t>2025-02-13T13:30:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-MedicationRequest.xlsx
+++ b/StructureDefinition-MedicationRequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-13T13:30:29+00:00</t>
+    <t>2025-02-18T14:04:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-MedicationRequest.xlsx
+++ b/StructureDefinition-MedicationRequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T14:04:23+00:00</t>
+    <t>2025-02-24T11:20:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-MedicationRequest.xlsx
+++ b/StructureDefinition-MedicationRequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T11:20:06+00:00</t>
+    <t>2025-02-24T11:23:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-MedicationRequest.xlsx
+++ b/StructureDefinition-MedicationRequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T11:23:09+00:00</t>
+    <t>2025-02-24T11:25:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-MedicationRequest.xlsx
+++ b/StructureDefinition-MedicationRequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T11:25:44+00:00</t>
+    <t>2025-02-24T11:27:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-MedicationRequest.xlsx
+++ b/StructureDefinition-MedicationRequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T11:27:07+00:00</t>
+    <t>2025-02-24T13:31:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-MedicationRequest.xlsx
+++ b/StructureDefinition-MedicationRequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T13:31:19+00:00</t>
+    <t>2025-02-24T15:55:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-MedicationRequest.xlsx
+++ b/StructureDefinition-MedicationRequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T15:55:23+00:00</t>
+    <t>2025-02-24T16:22:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-MedicationRequest.xlsx
+++ b/StructureDefinition-MedicationRequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T16:22:43+00:00</t>
+    <t>2025-02-25T09:38:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-MedicationRequest.xlsx
+++ b/StructureDefinition-MedicationRequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-25T09:38:10+00:00</t>
+    <t>2025-02-25T09:39:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-MedicationRequest.xlsx
+++ b/StructureDefinition-MedicationRequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-25T09:39:04+00:00</t>
+    <t>2025-02-25T20:48:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-MedicationRequest.xlsx
+++ b/StructureDefinition-MedicationRequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-25T20:48:56+00:00</t>
+    <t>2025-02-25T21:05:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-MedicationRequest.xlsx
+++ b/StructureDefinition-MedicationRequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-25T21:05:22+00:00</t>
+    <t>2025-02-26T07:46:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-MedicationRequest.xlsx
+++ b/StructureDefinition-MedicationRequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-26T07:46:44+00:00</t>
+    <t>2025-02-26T13:03:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-MedicationRequest.xlsx
+++ b/StructureDefinition-MedicationRequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-26T13:03:44+00:00</t>
+    <t>2025-02-26T13:09:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-MedicationRequest.xlsx
+++ b/StructureDefinition-MedicationRequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-26T13:09:25+00:00</t>
+    <t>2025-02-26T14:34:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-MedicationRequest.xlsx
+++ b/StructureDefinition-MedicationRequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-26T14:34:33+00:00</t>
+    <t>2025-02-26T14:37:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-MedicationRequest.xlsx
+++ b/StructureDefinition-MedicationRequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-26T14:37:20+00:00</t>
+    <t>2025-02-28T09:54:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-MedicationRequest.xlsx
+++ b/StructureDefinition-MedicationRequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-28T09:54:46+00:00</t>
+    <t>2025-02-28T10:33:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-MedicationRequest.xlsx
+++ b/StructureDefinition-MedicationRequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-28T10:33:33+00:00</t>
+    <t>2025-02-28T10:57:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-MedicationRequest.xlsx
+++ b/StructureDefinition-MedicationRequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-28T10:57:51+00:00</t>
+    <t>2025-02-28T11:01:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-MedicationRequest.xlsx
+++ b/StructureDefinition-MedicationRequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-28T11:01:07+00:00</t>
+    <t>2025-02-28T11:11:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-MedicationRequest.xlsx
+++ b/StructureDefinition-MedicationRequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-28T11:11:13+00:00</t>
+    <t>2025-02-28T11:13:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-MedicationRequest.xlsx
+++ b/StructureDefinition-MedicationRequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-28T11:13:38+00:00</t>
+    <t>2025-02-28T11:38:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-MedicationRequest.xlsx
+++ b/StructureDefinition-MedicationRequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-28T11:38:05+00:00</t>
+    <t>2025-02-28T11:39:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-MedicationRequest.xlsx
+++ b/StructureDefinition-MedicationRequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-28T11:39:24+00:00</t>
+    <t>2025-02-28T11:59:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-MedicationRequest.xlsx
+++ b/StructureDefinition-MedicationRequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-28T11:59:16+00:00</t>
+    <t>2025-03-03T08:47:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-MedicationRequest.xlsx
+++ b/StructureDefinition-MedicationRequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-03T08:47:24+00:00</t>
+    <t>2025-03-04T09:51:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-MedicationRequest.xlsx
+++ b/StructureDefinition-MedicationRequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-04T09:51:39+00:00</t>
+    <t>2025-03-04T10:31:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-MedicationRequest.xlsx
+++ b/StructureDefinition-MedicationRequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-04T10:31:42+00:00</t>
+    <t>2025-03-05T06:48:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-MedicationRequest.xlsx
+++ b/StructureDefinition-MedicationRequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-05T06:48:27+00:00</t>
+    <t>2025-03-05T13:19:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-MedicationRequest.xlsx
+++ b/StructureDefinition-MedicationRequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-05T13:19:54+00:00</t>
+    <t>2025-03-05T13:45:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-MedicationRequest.xlsx
+++ b/StructureDefinition-MedicationRequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-05T13:45:25+00:00</t>
+    <t>2025-03-05T16:01:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-MedicationRequest.xlsx
+++ b/StructureDefinition-MedicationRequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-05T16:01:47+00:00</t>
+    <t>2025-03-06T16:40:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-MedicationRequest.xlsx
+++ b/StructureDefinition-MedicationRequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-06T16:40:55+00:00</t>
+    <t>2025-03-09T10:18:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-MedicationRequest.xlsx
+++ b/StructureDefinition-MedicationRequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-09T10:18:56+00:00</t>
+    <t>2025-03-09T10:31:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-MedicationRequest.xlsx
+++ b/StructureDefinition-MedicationRequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-09T10:31:47+00:00</t>
+    <t>2025-03-10T07:49:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-MedicationRequest.xlsx
+++ b/StructureDefinition-MedicationRequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-10T07:49:31+00:00</t>
+    <t>2025-03-10T07:56:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-MedicationRequest.xlsx
+++ b/StructureDefinition-MedicationRequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-10T07:56:47+00:00</t>
+    <t>2025-03-12T11:31:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-MedicationRequest.xlsx
+++ b/StructureDefinition-MedicationRequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-12T11:31:39+00:00</t>
+    <t>2025-03-12T11:55:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-MedicationRequest.xlsx
+++ b/StructureDefinition-MedicationRequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-12T11:55:43+00:00</t>
+    <t>2025-03-12T11:57:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-MedicationRequest.xlsx
+++ b/StructureDefinition-MedicationRequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-12T11:57:23+00:00</t>
+    <t>2025-03-13T10:18:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-MedicationRequest.xlsx
+++ b/StructureDefinition-MedicationRequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-13T10:18:09+00:00</t>
+    <t>2025-03-18T08:10:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-MedicationRequest.xlsx
+++ b/StructureDefinition-MedicationRequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-18T08:10:21+00:00</t>
+    <t>2025-03-18T10:21:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-MedicationRequest.xlsx
+++ b/StructureDefinition-MedicationRequest.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.12.0</t>
+    <t>1.13.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-18T10:21:48+00:00</t>
+    <t>2025-03-18T10:31:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-MedicationRequest.xlsx
+++ b/StructureDefinition-MedicationRequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-18T10:31:44+00:00</t>
+    <t>2025-03-18T13:21:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-MedicationRequest.xlsx
+++ b/StructureDefinition-MedicationRequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-18T13:21:59+00:00</t>
+    <t>2025-03-18T14:10:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-MedicationRequest.xlsx
+++ b/StructureDefinition-MedicationRequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-18T14:10:18+00:00</t>
+    <t>2025-03-24T10:28:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-MedicationRequest.xlsx
+++ b/StructureDefinition-MedicationRequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-24T10:28:29+00:00</t>
+    <t>2025-03-24T10:49:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-MedicationRequest.xlsx
+++ b/StructureDefinition-MedicationRequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-24T10:49:00+00:00</t>
+    <t>2025-03-24T11:21:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-MedicationRequest.xlsx
+++ b/StructureDefinition-MedicationRequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-24T11:21:14+00:00</t>
+    <t>2025-03-24T11:37:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-MedicationRequest.xlsx
+++ b/StructureDefinition-MedicationRequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-24T11:37:37+00:00</t>
+    <t>2025-04-01T10:33:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-MedicationRequest.xlsx
+++ b/StructureDefinition-MedicationRequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-01T10:33:26+00:00</t>
+    <t>2025-04-01T10:36:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-MedicationRequest.xlsx
+++ b/StructureDefinition-MedicationRequest.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.13.0</t>
+    <t>1.14.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-01T10:36:45+00:00</t>
+    <t>2025-04-01T10:40:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-MedicationRequest.xlsx
+++ b/StructureDefinition-MedicationRequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-01T10:40:06+00:00</t>
+    <t>2025-04-01T11:02:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-MedicationRequest.xlsx
+++ b/StructureDefinition-MedicationRequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-01T11:02:34+00:00</t>
+    <t>2025-04-07T09:57:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-MedicationRequest.xlsx
+++ b/StructureDefinition-MedicationRequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-07T09:57:36+00:00</t>
+    <t>2025-04-07T10:44:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-MedicationRequest.xlsx
+++ b/StructureDefinition-MedicationRequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-07T10:44:48+00:00</t>
+    <t>2025-04-07T14:17:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-MedicationRequest.xlsx
+++ b/StructureDefinition-MedicationRequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-07T14:17:30+00:00</t>
+    <t>2025-04-09T20:29:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-MedicationRequest.xlsx
+++ b/StructureDefinition-MedicationRequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-09T20:29:26+00:00</t>
+    <t>2025-04-09T20:35:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-MedicationRequest.xlsx
+++ b/StructureDefinition-MedicationRequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-09T20:35:07+00:00</t>
+    <t>2025-04-09T22:25:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-MedicationRequest.xlsx
+++ b/StructureDefinition-MedicationRequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-09T22:25:52+00:00</t>
+    <t>2025-04-09T23:03:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
